--- a/src/AVLStudentManagement.App/data/HoSoSinhVien.xlsx
+++ b/src/AVLStudentManagement.App/data/HoSoSinhVien.xlsx
@@ -59,832 +59,1822 @@
     <x:t>NgayCapNhat</x:t>
   </x:si>
   <x:si>
-    <x:t>12345678</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Chí Bảo</x:t>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Trọng Long</x:t>
   </x:si>
   <x:si>
     <x:t>Nam</x:t>
   </x:si>
   <x:si>
-    <x:t>999999999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abc@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0999999999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>abc, dhajdhfasfs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22CNTT1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Công nghệ thông tin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DangHoc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Minh Trung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200000220</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011001@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>88 Trần Hưng Đạo, Đà Nẵng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22CNTT2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Thị Ngân</x:t>
+    <x:t>089207842301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>longht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0980433027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường Mỹ Bình, Thành phố Long Xuyên, Tỉnh An Giang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trường Kỹ thuật và Công nghệ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đang học</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Thu Ngọc</x:t>
   </x:si>
   <x:si>
     <x:t>Nữ</x:t>
   </x:si>
   <x:si>
-    <x:t>079200032540</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011005@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0970596166</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Đức Hùng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200063987</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011009@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0956333468</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45 Lê Lợi, Quận 1, TP.HCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22CNTT3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Hữu Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200095881</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011013@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0940896843</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Thu Vy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200127459</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011017@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0966342782</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaoLuu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trần Khánh Anh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200159357</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011021@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0957510797</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hoàng Quốc Huy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200190306</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011025@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0968060066</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Thị Hà</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200222150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011029@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0917180913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7 Phan Chu Trinh, Huế</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nguyễn Hữu Trung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200254333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011033@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0918427418</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23 Hai Bà Trưng, Hà Nội</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011037</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Thu Anh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200285088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011037@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>150 Nguyễn Huệ, Cần Thơ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vũ Văn Dũng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200317519</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011041@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0943231465</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Mai Trang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200348559</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011045@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0926486947</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Thị Ngân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200380621</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22011049@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0978540538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Phương Anh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200008008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021002@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0954458592</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22KT1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kinh tế</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ThoiHoc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vũ Đức Trung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200039838</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021006@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0984439090</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22KT2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Ngọc Linh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200071887</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021010@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Văn Huy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200103196</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021014@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0984630123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12 Nguyễn Trãi, Quận 5, TP.HCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Ngọc My</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200135063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021018@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0947143608</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Văn Phúc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200167234</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021022@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0923213482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Khánh Lan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200198791</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021026@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0928657950</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Mai My</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200230492</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021030@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0914450155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Văn Tuấn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200261736</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021034@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0959725529</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nguyễn Minh Long</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200293004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021038@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0994225757</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021042</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Thanh Nam</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200324955</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021042@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0910238152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trần Hữu Nam</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200356441</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021046@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021050</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Văn Dũng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200388247</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22021050@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0984534878</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Quốc Khoa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200016231</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031003@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0989031909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22NN2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ngoại ngữ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Khánh Hà</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200048187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031007@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0942915419</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22NN1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Văn Hùng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200079996</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031011@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0951980366</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DaTotNghiep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Quốc Long</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200111796</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031015@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0914182521</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hoàng Hữu Nam</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200143040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031019@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Thị Lan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200174538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031023@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0985090300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Phương Vy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200206573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031027@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0960040683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Phương My</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200238097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031031@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0913170052</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trần Hữu Khoa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200269271</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031035@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0988361264</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trần Thu Thảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200300924</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031039@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0950931144</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Thị Anh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200333057</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031043@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0993237286</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Văn Khoa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200364569</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22031047@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0967231095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Đức Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200023885</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041004@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0978282038</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22CK1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cơ khí</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Thanh Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200055850</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041008@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0911245706</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Minh Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200087679</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041012@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0988826439</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Minh Long</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200119225</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041016@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0965138316</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vũ Khánh Vy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200151067</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041020@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0962228404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trần Đức Phúc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200182727</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041024@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0956849800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Ngọc Anh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200214748</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041028@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Thanh Hùng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200245667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041032@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0933519430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22CK2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Phương Anh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200277535</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041036@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0919889076</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Đức Khoa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200308851</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041040@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0951399575</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vũ Phương Lan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200341417</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041044@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0972566540</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Thị Trang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>079200372330</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22041048@student.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0989472504</x:t>
+    <x:t>086307136141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ngocvt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0321527788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Phú Hòa, Xã Phú Thịnh, Huyện Tam Bình, Tỉnh Vĩnh Long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trường Y Dược</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Danh Vi Rây</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206051573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raydv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0976231518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khóm 4, Phường 3, Thành phố Trà Vinh, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Ngôn ngữ Khmer Nam Bộ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Thanh Nhi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307573543</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhitt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0900911131</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Sóc Xoài, Xã Mỹ Long Bắc, Huyện Cầu Ngang, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25NNB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Ngoại ngữ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Thanh Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089305263995</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongtt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0767796963</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Trọng Hậu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205460345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hautt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0706674128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Sóc Ruộng, Xã Đa Lộc, Huyện Châu Thành, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cao Gia Nghĩa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086205850671</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nghiacg@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0761473048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phạm Thị Thảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306296531</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaopt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0794492684</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Long Hậu, Xã Long Vĩnh, Huyện Duyên Hải, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Thu Duyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306506337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyenlt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0326320632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Ba Se, Xã Châu Điền, Huyện Cầu Kè, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Kim Tú</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307660952</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tunk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0942808460</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Ngãi Xuyên, Xã Ngãi Xuyên, Huyện Trà Cú, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Nông nghiệp - Thủy sản</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Minh Bảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205625244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baohm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0970440837</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Nhị Trường, Xã Nhị Trường, Huyện Cầu Ngang, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trường Kinh tế, Luật</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Thị Sa Rây</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306660163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raycts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0705596382</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Thu Tú</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086306508948</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tudt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0383495362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 2, Thành phố Vĩnh Long, Tỉnh Vĩnh Long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Danh Thị Sô Phia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306635388</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phiadts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0763503120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Mỹ Cẩm, Xã Mỹ Cẩm, Huyện Càng Long, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Hồng Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089306187368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vyth@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0972288261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bảo lưu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Thị Ngọc Thu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092306333499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thuctn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0909492010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường An Khánh, Quận Ninh Kiều, Thành phố Cần Thơ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Anh Kiệt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206511902</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kietba@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0765481323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24SPB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trường Sư phạm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Cẩm Nhung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307782381</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhunglc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0760121877</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Bích Duyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307188888</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyenlb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0907667529</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Tập Ngãi, Xã Tập Ngãi, Huyện Tiểu Cần, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Đức Lộc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206957866</x:t>
+  </x:si>
+  <x:si>
+    <x:t>locpd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323569423</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Chợ, Xã Bình Phú, Huyện Càng Long, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Yến Linh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089306185755</x:t>
+  </x:si>
+  <x:si>
+    <x:t>linhdy@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0704865793</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NNB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Văn Hiếu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207028723</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hieuhv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0708513006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25SPB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Cẩm Trang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095305101433</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tranghc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0933093670</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 3, Thành phố Bạc Liêu, Tỉnh Bạc Liêu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Hoàng Trung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206245323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trungch@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0794333756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Cây Xoài, Xã Hòa Ân, Huyện Cầu Kè, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Mỹ Trâm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092305585490</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tramdm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323541573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Văn Thịnh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205351969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thinhvv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0320618527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khóm 2, Phường 7, Thành phố Trà Vinh, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Cẩm Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>091305458272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vydc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0911557161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường Vĩnh Thanh, Thành phố Rạch Giá, Tỉnh Kiên Giang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Ngọc Trang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307681088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trangtn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0935679527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ngô Công Phước</x:t>
+  </x:si>
+  <x:si>
+    <x:t>083206515146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuocnc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323792853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp An Hội, Xã An Hóa, Huyện Châu Thành, Tỉnh Bến Tre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Thu Ngọc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092306547883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ngocht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0971261486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thôi học</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Ngọc Thảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307468467</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaohn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0944797658</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Kim Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305525236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanpk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0381915053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Tuấn Lộc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205137234</x:t>
+  </x:si>
+  <x:si>
+    <x:t>locht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0766112392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Thanh Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305057488</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nganht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0973442955</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Hồng Phượng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092307427774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuonglh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0794470273</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mai Thị Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095306065910</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanmt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0914216394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Thanh Thiện</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207500796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thienpt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0327731674</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Gia Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206127305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duytg@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0987988924</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Bà Mi, Xã Tập Sơn, Huyện Trà Cú, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thạch Hoàng Pha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206168967</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phath@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0764199317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Thanh Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306908861</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nganvt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0324951108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Yến Châu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306402430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>chauhy@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323346251</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thạch Thị Ngọc Thu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094306995326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thuttn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0911819945</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 5, Thị xã Vĩnh Châu, Tỉnh Sóc Trăng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Ngọc Duyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094306526218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyentn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0919559096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Minh Hậu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207587156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>haulm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0385793464</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Hoàng Phát</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205202547</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phatlh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0386734039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Kim Nhi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>087306305906</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhidk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0978064729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 1, Thành phố Cao Lãnh, Tỉnh Đồng Tháp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Yến Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307606855</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maity@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0763776371</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Thu Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306459796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vyht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0934469754</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Anh Trung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205242230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trungta@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0948157871</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Công Thịnh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089205337071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thinhdc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0980653344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Thúy Phượng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307050145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuongdt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0906637509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Hồng Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094305029747</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanth@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0351950522</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Diễm Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306158182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maidd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0324016802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Hồng Phượng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305222815</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuongvh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0385522581</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Nhật Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094207436366</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyvn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0948971062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Hòa Thành, Xã Hòa Tú, Huyện Mỹ Xuyên, Tỉnh Sóc Trăng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Quốc Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>096207549655</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duydq@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0901928766</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 9, Thành phố Cà Mau, Tỉnh Cà Mau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Thanh Phát</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094207922237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phattt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0984724383</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ngô Mỹ Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094307230815</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongnm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0768848324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Hồng Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092307615754</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongdh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0989209082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Thu Tú</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086307885833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tubt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0791553778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Tuấn Hiếu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>091205406217</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hieudt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0351779197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Bích Thảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086305375926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaolb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0387106113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Anh Long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206223477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>longla@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0937337507</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Kim Phượng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306558147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuonglk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0945858133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Đức Bảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205079152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baohd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0935166077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Ngọc Như</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306591393</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhubn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0976364796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Công Khang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095207717245</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khanglc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0765543972</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Thị Sô Ka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306519287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kalts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0356284533</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Quốc Huy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207457636</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huybq@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0358478239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Yến Trâm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086307418213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tramcy@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0980140725</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cao Kim Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089306828375</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maick@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0933961878</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Hoàng Phát</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086207501341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phatdh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0328273063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Trọng Hiếu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205501111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hieuht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0383329486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Diễm Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306708343</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongtd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0799434505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đỗ Bích Nhung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306230754</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhungdb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0705573756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Minh Lộc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>087206547340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>locvm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0906634998</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Gia Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207337323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duypg@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0972945557</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mai Thanh Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>091307189570</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanmt2@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0704376698</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mai Diễm Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095306682900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maimd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0705377769</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Thanh Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307183024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vypt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0977866596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Mỹ Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086306551414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongpm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0321101268</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306635880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phiadts2@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0985002508</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Bích Ngọc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>083307860204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ngoctb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0354270093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phạm Hoàng Tài</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206869893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>taiph@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0986334014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sơn Sa Ruôl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205786003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ruolss@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0768832759</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Phương Châu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089305962940</x:t>
+  </x:si>
+  <x:si>
+    <x:t>chautp@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0350865639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Nhật Long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206810306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>longbn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0708690541</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phạm Thu Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306115440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nganpt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0385117673</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Phương Lan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307591487</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lanhp@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0948577595</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Bích Nhung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305174514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhunglb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0703121935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Hiếu Trung, Xã Hiếu Tử, Huyện Tiểu Cần, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sơn Thị Sô Ka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305867970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kasts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0918529360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Thị Trâm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305170110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tramtt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0946583809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sơn Rô Tha Na</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205905600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nasrt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0767410798</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đỗ Ngọc Nhi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094306888995</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhidn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0941476650</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Công Thiện</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092205639988</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thienlc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0981384507</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ngô Anh Thiện</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206136968</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thienna@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0905452018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cao Ngọc Như</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095305413982</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhucn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0355398125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Thanh Bảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206462993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baont@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0917102655</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Diễm Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092305851812</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ngancd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0768437124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Vi Rây</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207043792</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raycv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0326151026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25NNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21NNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21NNB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22NNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22NNB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23NNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23NNB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21SPB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22SPB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23SPB</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1295,22 +2285,22 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N52"/>
+  <x:dimension ref="A1:N101"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.996339" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="8.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="25.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="30.139196" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="8.710625" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="19.282054" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="7.853482" style="2" customWidth="1"/>
-    <x:col min="13" max="14" width="19.139196" style="3" customWidth="1"/>
+    <x:col min="1" max="1" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.710625" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.710625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="60.710625" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11.710625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30.710625" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="8.710625" style="2" customWidth="1"/>
+    <x:col min="13" max="14" width="20.710625" style="3" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:14" s="4" customFormat="1">
@@ -1365,7 +2355,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>40095</x:v>
+        <x:v>39439</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>16</x:v>
@@ -1392,13 +2382,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L2" s="2">
-        <x:v>3</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="M2" s="3">
-        <x:v>46304.380848044</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N2" s="3">
-        <x:v>46304.380848044</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
@@ -1409,157 +2399,157 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>38168</x:v>
+        <x:v>39226</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L3" s="2">
-        <x:v>3.98</x:v>
+        <x:v>7.26</x:v>
       </x:c>
       <x:c r="M3" s="3">
-        <x:v>45901.3333333333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N3" s="3">
-        <x:v>45901.3333333333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>38865</x:v>
+        <x:v>38730</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L4" s="2">
-        <x:v>1.1</x:v>
+        <x:v>6.82</x:v>
       </x:c>
       <x:c r="M4" s="3">
-        <x:v>45901.3527777778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N4" s="3">
-        <x:v>45901.3527777778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:14">
       <x:c r="A5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>38704</x:v>
+        <x:v>39270</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L5" s="2">
-        <x:v>1.44</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="M5" s="3">
-        <x:v>45901.3722222222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N5" s="3">
-        <x:v>45901.3722222222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:14">
       <x:c r="A6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>38316</x:v>
+        <x:v>38696</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
         <x:v>22</x:v>
@@ -1568,86 +2558,86 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L6" s="2">
-        <x:v>2.09</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="M6" s="3">
-        <x:v>45901.3916666667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N6" s="3">
-        <x:v>45901.3916666667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:14">
       <x:c r="A7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>38302</x:v>
+        <x:v>38400</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L7" s="2">
-        <x:v>1.6</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="M7" s="3">
-        <x:v>45901.4111111111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N7" s="3">
-        <x:v>45901.4111111111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:14">
       <x:c r="A8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>38003</x:v>
+        <x:v>38583</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
         <x:v>22</x:v>
@@ -1656,86 +2646,86 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L8" s="2">
-        <x:v>3.14</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="M8" s="3">
-        <x:v>45901.4305555556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N8" s="3">
-        <x:v>45901.4305555556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>38333</x:v>
+        <x:v>39055</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L9" s="2">
-        <x:v>3.63</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="M9" s="3">
-        <x:v>45901.45</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N9" s="3">
-        <x:v>45901.45</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>38006</x:v>
+        <x:v>38791</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
         <x:v>22</x:v>
@@ -1744,1861 +2734,4017 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L10" s="2">
-        <x:v>3.78</x:v>
+        <x:v>6.19</x:v>
       </x:c>
       <x:c r="M10" s="3">
-        <x:v>45901.4694444444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N10" s="3">
-        <x:v>45901.4694444444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>38127</x:v>
+        <x:v>39328</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L11" s="2">
-        <x:v>1.99</x:v>
+        <x:v>7.66</x:v>
       </x:c>
       <x:c r="M11" s="3">
-        <x:v>45901.4888888889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N11" s="3">
-        <x:v>45901.4888888889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>38496</x:v>
+        <x:v>38494</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L12" s="2">
-        <x:v>1.7</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="M12" s="3">
-        <x:v>45901.5083333333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N12" s="3">
-        <x:v>45901.5083333333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>38078</x:v>
+        <x:v>38767</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L13" s="2">
-        <x:v>2.67</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="M13" s="3">
-        <x:v>45901.5277777778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N13" s="3">
-        <x:v>45901.5277777778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>38505</x:v>
+        <x:v>38732</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L14" s="2">
-        <x:v>2.34</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="M14" s="3">
-        <x:v>45901.5472222222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N14" s="3">
-        <x:v>45901.5472222222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>38099</x:v>
+        <x:v>38948</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L15" s="2">
-        <x:v>1.41</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="M15" s="3">
-        <x:v>45901.5666666667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N15" s="3">
-        <x:v>45901.5666666667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:14">
       <x:c r="A16" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>38603</x:v>
+        <x:v>38973</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="L16" s="2">
-        <x:v>3.64</x:v>
+        <x:v>6.85</x:v>
       </x:c>
       <x:c r="M16" s="3">
-        <x:v>45901.3381944444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N16" s="3">
-        <x:v>45901.3381944444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:14">
       <x:c r="A17" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>38430</x:v>
+        <x:v>38944</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L17" s="2">
-        <x:v>1.67</x:v>
+        <x:v>6.16</x:v>
       </x:c>
       <x:c r="M17" s="3">
-        <x:v>45901.3576388889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N17" s="3">
-        <x:v>45901.3576388889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:14">
       <x:c r="A18" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>38053</x:v>
+        <x:v>38902</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L18" s="2">
-        <x:v>2.7</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="M18" s="3">
-        <x:v>45901.3770833333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N18" s="3">
-        <x:v>45901.3770833333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:14">
       <x:c r="A19" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>38720</x:v>
+        <x:v>39342</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L19" s="2">
-        <x:v>2.12</x:v>
+        <x:v>7.47</x:v>
       </x:c>
       <x:c r="M19" s="3">
-        <x:v>45901.3965277778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N19" s="3">
-        <x:v>45901.3965277778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:14">
       <x:c r="A20" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>38808</x:v>
+        <x:v>39340</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L20" s="2">
-        <x:v>1.22</x:v>
+        <x:v>7.26</x:v>
       </x:c>
       <x:c r="M20" s="3">
-        <x:v>45901.4159722222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N20" s="3">
-        <x:v>45901.4159722222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:14">
       <x:c r="A21" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>38307</x:v>
+        <x:v>38738</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L21" s="2">
-        <x:v>3.21</x:v>
+        <x:v>7.27</x:v>
       </x:c>
       <x:c r="M21" s="3">
-        <x:v>45901.4354166667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N21" s="3">
-        <x:v>45901.4354166667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:14">
       <x:c r="A22" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>38446</x:v>
+        <x:v>38786</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L22" s="2">
-        <x:v>2.96</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="M22" s="3">
-        <x:v>45901.4548611111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N22" s="3">
-        <x:v>45901.4548611111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:14">
       <x:c r="A23" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>38757</x:v>
+        <x:v>39195</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L23" s="2">
-        <x:v>3.29</x:v>
+        <x:v>6.76</x:v>
       </x:c>
       <x:c r="M23" s="3">
-        <x:v>45901.4743055556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N23" s="3">
-        <x:v>45901.4743055556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:14">
       <x:c r="A24" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>38143</x:v>
+        <x:v>38603</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L24" s="2">
-        <x:v>1.52</x:v>
+        <x:v>6.68</x:v>
       </x:c>
       <x:c r="M24" s="3">
-        <x:v>45901.49375</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N24" s="3">
-        <x:v>45901.49375</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:14">
       <x:c r="A25" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>38162</x:v>
+        <x:v>38799</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L25" s="2">
-        <x:v>2.55</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="M25" s="3">
-        <x:v>45901.5131944444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N25" s="3">
-        <x:v>45901.5131944444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:14">
       <x:c r="A26" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>38785</x:v>
+        <x:v>38599</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L26" s="2">
-        <x:v>3.03</x:v>
+        <x:v>6.62</x:v>
       </x:c>
       <x:c r="M26" s="3">
-        <x:v>45901.5326388889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N26" s="3">
-        <x:v>45901.5326388889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:14">
       <x:c r="A27" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>38112</x:v>
+        <x:v>38489</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="G27" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H27" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I27" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L27" s="2">
-        <x:v>2.51</x:v>
+        <x:v>7.83</x:v>
       </x:c>
       <x:c r="M27" s="3">
-        <x:v>45901.5520833333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N27" s="3">
-        <x:v>45901.5520833333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:14">
       <x:c r="A28" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>38246</x:v>
+        <x:v>38670</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L28" s="2">
-        <x:v>3.26</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="M28" s="3">
-        <x:v>45901.5715277778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N28" s="3">
-        <x:v>45901.5715277778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:14">
       <x:c r="A29" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>38849</x:v>
+        <x:v>39290</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L29" s="2">
-        <x:v>3.56</x:v>
+        <x:v>7.97</x:v>
       </x:c>
       <x:c r="M29" s="3">
-        <x:v>45901.3430555556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N29" s="3">
-        <x:v>45901.3430555556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:14">
       <x:c r="A30" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>38209</x:v>
+        <x:v>38933</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L30" s="2">
-        <x:v>2.71</x:v>
+        <x:v>5.43</x:v>
       </x:c>
       <x:c r="M30" s="3">
-        <x:v>45901.3625</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N30" s="3">
-        <x:v>45901.3625</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:14">
       <x:c r="A31" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>38479</x:v>
+        <x:v>38843</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="L31" s="2">
-        <x:v>1.93</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="M31" s="3">
-        <x:v>45901.3819444444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N31" s="3">
-        <x:v>45901.3819444444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:14">
       <x:c r="A32" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>38359</x:v>
+        <x:v>39115</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L32" s="2">
-        <x:v>2.04</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="M32" s="3">
-        <x:v>45901.4013888889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N32" s="3">
-        <x:v>45901.4013888889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:14">
       <x:c r="A33" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>38535</x:v>
+        <x:v>38403</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L33" s="2">
-        <x:v>3.36</x:v>
+        <x:v>7.12</x:v>
       </x:c>
       <x:c r="M33" s="3">
-        <x:v>45901.4208333333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N33" s="3">
-        <x:v>45901.4208333333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:14">
       <x:c r="A34" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>38131</x:v>
+        <x:v>38617</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="L34" s="2">
-        <x:v>2.92</x:v>
+        <x:v>8.31</x:v>
       </x:c>
       <x:c r="M34" s="3">
-        <x:v>45901.4402777778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N34" s="3">
-        <x:v>45901.4402777778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:14">
       <x:c r="A35" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>38167</x:v>
+        <x:v>38546</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="2">
-        <x:v>2.42</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="M35" s="3">
-        <x:v>45901.4597222222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N35" s="3">
-        <x:v>45901.4597222222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:14">
       <x:c r="A36" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>37994</x:v>
+        <x:v>39279</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L36" s="2">
-        <x:v>2.9</x:v>
+        <x:v>7.01</x:v>
       </x:c>
       <x:c r="M36" s="3">
-        <x:v>45901.4791666667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N36" s="3">
-        <x:v>45901.4791666667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:14">
       <x:c r="A37" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>38877</x:v>
+        <x:v>38972</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L37" s="2">
-        <x:v>3.58</x:v>
+        <x:v>8.68</x:v>
       </x:c>
       <x:c r="M37" s="3">
-        <x:v>45901.4986111111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N37" s="3">
-        <x:v>45901.4986111111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:14">
       <x:c r="A38" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>38247</x:v>
+        <x:v>39175</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="J38" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K38" s="0" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="F38" s="0" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G38" s="0" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H38" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I38" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="J38" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="K38" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="L38" s="2">
-        <x:v>1.61</x:v>
+        <x:v>6.22</x:v>
       </x:c>
       <x:c r="M38" s="3">
-        <x:v>45901.5180555556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N38" s="3">
-        <x:v>45901.5180555556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:14">
       <x:c r="A39" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>38592</x:v>
+        <x:v>38943</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L39" s="2">
-        <x:v>3</x:v>
+        <x:v>6.94</x:v>
       </x:c>
       <x:c r="M39" s="3">
-        <x:v>45901.5375</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N39" s="3">
-        <x:v>45901.5375</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:14">
       <x:c r="A40" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>38310</x:v>
+        <x:v>38798</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L40" s="2">
-        <x:v>3.79</x:v>
+        <x:v>6.51</x:v>
       </x:c>
       <x:c r="M40" s="3">
-        <x:v>45901.5569444444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N40" s="3">
-        <x:v>45901.5569444444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:14">
       <x:c r="A41" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>38361</x:v>
+        <x:v>39000</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="H41" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="I41" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L41" s="2">
-        <x:v>3.15</x:v>
+        <x:v>8.53</x:v>
       </x:c>
       <x:c r="M41" s="3">
-        <x:v>45901.3479166667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N41" s="3">
-        <x:v>45901.3479166667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:14">
       <x:c r="A42" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>38686</x:v>
+        <x:v>38832</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L42" s="2">
-        <x:v>2.64</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="M42" s="3">
-        <x:v>45901.3673611111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N42" s="3">
-        <x:v>45901.3673611111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:14">
       <x:c r="A43" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>38115</x:v>
+        <x:v>38838</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L43" s="2">
-        <x:v>1.16</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="M43" s="3">
-        <x:v>45901.3868055556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N43" s="3">
-        <x:v>45901.3868055556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:14">
       <x:c r="A44" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>38663</x:v>
+        <x:v>38933</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L44" s="2">
-        <x:v>1.14</x:v>
+        <x:v>8.58</x:v>
       </x:c>
       <x:c r="M44" s="3">
-        <x:v>45901.40625</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N44" s="3">
-        <x:v>45901.40625</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:14">
       <x:c r="A45" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>38519</x:v>
+        <x:v>39326</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="I45" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L45" s="2">
-        <x:v>2.17</x:v>
+        <x:v>6.79</x:v>
       </x:c>
       <x:c r="M45" s="3">
-        <x:v>45901.4256944444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N45" s="3">
-        <x:v>45901.4256944444</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:14">
       <x:c r="A46" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>38216</x:v>
+        <x:v>38402</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L46" s="2">
-        <x:v>1.4</x:v>
+        <x:v>6.46</x:v>
       </x:c>
       <x:c r="M46" s="3">
-        <x:v>45901.4451388889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N46" s="3">
-        <x:v>45901.4451388889</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:14">
       <x:c r="A47" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>38690</x:v>
+        <x:v>38971</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L47" s="2">
-        <x:v>3.75</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="M47" s="3">
-        <x:v>45901.4645833333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N47" s="3">
-        <x:v>45901.4645833333</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:14">
       <x:c r="A48" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>38721</x:v>
+        <x:v>39437</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L48" s="2">
-        <x:v>3.99</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="M48" s="3">
-        <x:v>45901.4840277778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N48" s="3">
-        <x:v>45901.4840277778</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:14">
       <x:c r="A49" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>38846</x:v>
+        <x:v>38890</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I49" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L49" s="2">
-        <x:v>2.24</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="M49" s="3">
-        <x:v>45901.5034722222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N49" s="3">
-        <x:v>45901.5034722222</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:14">
       <x:c r="A50" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>38475</x:v>
+        <x:v>38583</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I50" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="J50" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L50" s="2">
-        <x:v>1.56</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="M50" s="3">
-        <x:v>45901.5229166667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N50" s="3">
-        <x:v>45901.5229166667</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:14">
       <x:c r="A51" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>38563</x:v>
+        <x:v>38396</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J51" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L51" s="2">
-        <x:v>1.28</x:v>
+        <x:v>7.59</x:v>
       </x:c>
       <x:c r="M51" s="3">
-        <x:v>45901.5423611111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N51" s="3">
-        <x:v>45901.5423611111</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:14">
       <x:c r="A52" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>38620</x:v>
+        <x:v>39405</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I52" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J52" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="L52" s="2">
-        <x:v>3.8</x:v>
+        <x:v>7.71</x:v>
       </x:c>
       <x:c r="M52" s="3">
-        <x:v>45901.5618055556</x:v>
+        <x:v>46304.6390755903</x:v>
       </x:c>
       <x:c r="N52" s="3">
-        <x:v>45901.5618055556</x:v>
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:14">
+      <x:c r="A53" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="C53" s="1">
+        <x:v>38449</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J53" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L53" s="2">
+        <x:v>6.33</x:v>
+      </x:c>
+      <x:c r="M53" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N53" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:14">
+      <x:c r="A54" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="C54" s="1">
+        <x:v>38970</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="J54" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K54" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L54" s="2">
+        <x:v>6.65</x:v>
+      </x:c>
+      <x:c r="M54" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N54" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:14">
+      <x:c r="A55" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="C55" s="1">
+        <x:v>38363</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E55" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="J55" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K55" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L55" s="2">
+        <x:v>6.99</x:v>
+      </x:c>
+      <x:c r="M55" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N55" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:14">
+      <x:c r="A56" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="C56" s="1">
+        <x:v>39223</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E56" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J56" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K56" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L56" s="2">
+        <x:v>6.92</x:v>
+      </x:c>
+      <x:c r="M56" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N56" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:14">
+      <x:c r="A57" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="C57" s="1">
+        <x:v>39302</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E57" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="J57" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K57" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="L57" s="2">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="M57" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N57" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:14">
+      <x:c r="A58" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="C58" s="1">
+        <x:v>39412</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E58" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J58" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K58" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L58" s="2">
+        <x:v>8.2</x:v>
+      </x:c>
+      <x:c r="M58" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N58" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:14">
+      <x:c r="A59" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="C59" s="1">
+        <x:v>39371</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="I59" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="J59" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K59" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L59" s="2">
+        <x:v>7.62</x:v>
+      </x:c>
+      <x:c r="M59" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N59" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:14">
+      <x:c r="A60" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="C60" s="1">
+        <x:v>39099</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="J60" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K60" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L60" s="2">
+        <x:v>6.13</x:v>
+      </x:c>
+      <x:c r="M60" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N60" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:14">
+      <x:c r="A61" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="C61" s="1">
+        <x:v>39199</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="J61" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K61" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L61" s="2">
+        <x:v>6.78</x:v>
+      </x:c>
+      <x:c r="M61" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N61" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:14">
+      <x:c r="A62" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C62" s="1">
+        <x:v>38603</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="I62" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J62" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K62" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="L62" s="2">
+        <x:v>8.61</x:v>
+      </x:c>
+      <x:c r="M62" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N62" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:14">
+      <x:c r="A63" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="C63" s="1">
+        <x:v>38693</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J63" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K63" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L63" s="2">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="M63" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N63" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:14">
+      <x:c r="A64" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="C64" s="1">
+        <x:v>38834</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="J64" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K64" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="L64" s="2">
+        <x:v>7.6</x:v>
+      </x:c>
+      <x:c r="M64" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N64" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:14">
+      <x:c r="A65" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="C65" s="1">
+        <x:v>38988</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="J65" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K65" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L65" s="2">
+        <x:v>5.78</x:v>
+      </x:c>
+      <x:c r="M65" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N65" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:14">
+      <x:c r="A66" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="C66" s="1">
+        <x:v>38419</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="H66" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J66" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K66" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="L66" s="2">
+        <x:v>5.99</x:v>
+      </x:c>
+      <x:c r="M66" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N66" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:14">
+      <x:c r="A67" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="C67" s="1">
+        <x:v>38901</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="H67" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="J67" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K67" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L67" s="2">
+        <x:v>5.41</x:v>
+      </x:c>
+      <x:c r="M67" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N67" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:14">
+      <x:c r="A68" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C68" s="1">
+        <x:v>39218</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="H68" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="I68" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="J68" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K68" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L68" s="2">
+        <x:v>6.3</x:v>
+      </x:c>
+      <x:c r="M68" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N68" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:14">
+      <x:c r="A69" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="C69" s="1">
+        <x:v>38860</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="J69" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K69" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L69" s="2">
+        <x:v>6.57</x:v>
+      </x:c>
+      <x:c r="M69" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N69" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:14">
+      <x:c r="A70" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="C70" s="1">
+        <x:v>39389</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="H70" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I70" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="J70" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K70" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L70" s="2">
+        <x:v>7.08</x:v>
+      </x:c>
+      <x:c r="M70" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N70" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:14">
+      <x:c r="A71" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="C71" s="1">
+        <x:v>39258</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="G71" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="H71" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J71" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K71" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L71" s="2">
+        <x:v>7.01</x:v>
+      </x:c>
+      <x:c r="M71" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N71" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:14">
+      <x:c r="A72" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="C72" s="1">
+        <x:v>38921</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="G72" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="H72" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="J72" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K72" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L72" s="2">
+        <x:v>6.92</x:v>
+      </x:c>
+      <x:c r="M72" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N72" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:14">
+      <x:c r="A73" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="C73" s="1">
+        <x:v>39084</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="F73" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="G73" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="H73" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I73" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J73" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K73" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L73" s="2">
+        <x:v>7.65</x:v>
+      </x:c>
+      <x:c r="M73" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N73" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:14">
+      <x:c r="A74" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C74" s="1">
+        <x:v>38629</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="G74" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="H74" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J74" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K74" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L74" s="2">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="M74" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N74" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:14">
+      <x:c r="A75" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="C75" s="1">
+        <x:v>39037</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="G75" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="H75" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I75" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="J75" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K75" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L75" s="2">
+        <x:v>8.59</x:v>
+      </x:c>
+      <x:c r="M75" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N75" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:14">
+      <x:c r="A76" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="C76" s="1">
+        <x:v>38913</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="G76" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="H76" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J76" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K76" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L76" s="2">
+        <x:v>5.99</x:v>
+      </x:c>
+      <x:c r="M76" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N76" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:14">
+      <x:c r="A77" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="C77" s="1">
+        <x:v>38722</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="F77" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="G77" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="H77" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="J77" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K77" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L77" s="2">
+        <x:v>6.6</x:v>
+      </x:c>
+      <x:c r="M77" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N77" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:14">
+      <x:c r="A78" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C78" s="1">
+        <x:v>39409</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="G78" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="H78" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I78" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J78" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K78" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L78" s="2">
+        <x:v>6.65</x:v>
+      </x:c>
+      <x:c r="M78" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N78" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:14">
+      <x:c r="A79" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="C79" s="1">
+        <x:v>39304</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="H79" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="J79" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K79" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L79" s="2">
+        <x:v>7.09</x:v>
+      </x:c>
+      <x:c r="M79" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N79" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:14">
+      <x:c r="A80" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="C80" s="1">
+        <x:v>38986</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="G80" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="H80" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="I80" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="J80" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K80" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L80" s="2">
+        <x:v>8.48</x:v>
+      </x:c>
+      <x:c r="M80" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N80" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:14">
+      <x:c r="A81" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="C81" s="1">
+        <x:v>39404</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="G81" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="H81" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J81" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K81" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L81" s="2">
+        <x:v>7.62</x:v>
+      </x:c>
+      <x:c r="M81" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N81" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:14">
+      <x:c r="A82" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="C82" s="1">
+        <x:v>39015</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="H82" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="J82" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K82" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L82" s="2">
+        <x:v>7.93</x:v>
+      </x:c>
+      <x:c r="M82" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N82" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:14">
+      <x:c r="A83" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C83" s="1">
+        <x:v>38801</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="G83" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="H83" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J83" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K83" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L83" s="2">
+        <x:v>9.11</x:v>
+      </x:c>
+      <x:c r="M83" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N83" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:14">
+      <x:c r="A84" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="C84" s="1">
+        <x:v>39353</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="G84" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="H84" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="J84" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K84" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L84" s="2">
+        <x:v>5.54</x:v>
+      </x:c>
+      <x:c r="M84" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N84" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:14">
+      <x:c r="A85" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="C85" s="1">
+        <x:v>38824</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="G85" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="H85" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J85" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K85" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L85" s="2">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="M85" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N85" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:14">
+      <x:c r="A86" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="C86" s="1">
+        <x:v>38479</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="G86" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="H86" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J86" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K86" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L86" s="2">
+        <x:v>6.13</x:v>
+      </x:c>
+      <x:c r="M86" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N86" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:14">
+      <x:c r="A87" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="C87" s="1">
+        <x:v>38361</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="G87" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="H87" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J87" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K87" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L87" s="2">
+        <x:v>5.39</x:v>
+      </x:c>
+      <x:c r="M87" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N87" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:14">
+      <x:c r="A88" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="C88" s="1">
+        <x:v>38788</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="G88" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="H88" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="J88" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K88" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L88" s="2">
+        <x:v>8.59</x:v>
+      </x:c>
+      <x:c r="M88" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N88" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:14">
+      <x:c r="A89" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="C89" s="1">
+        <x:v>38951</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="G89" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="H89" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J89" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K89" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L89" s="2">
+        <x:v>6.14</x:v>
+      </x:c>
+      <x:c r="M89" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N89" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:14">
+      <x:c r="A90" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="C90" s="1">
+        <x:v>39271</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="G90" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="H90" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J90" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K90" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L90" s="2">
+        <x:v>6.44</x:v>
+      </x:c>
+      <x:c r="M90" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N90" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:14">
+      <x:c r="A91" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C91" s="1">
+        <x:v>38710</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="G91" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="H91" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="J91" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K91" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L91" s="2">
+        <x:v>8.78</x:v>
+      </x:c>
+      <x:c r="M91" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N91" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:14">
+      <x:c r="A92" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="C92" s="1">
+        <x:v>38468</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="G92" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="H92" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="J92" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K92" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L92" s="2">
+        <x:v>5.97</x:v>
+      </x:c>
+      <x:c r="M92" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N92" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:14">
+      <x:c r="A93" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="C93" s="1">
+        <x:v>38648</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="G93" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="H93" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="J93" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K93" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L93" s="2">
+        <x:v>7.79</x:v>
+      </x:c>
+      <x:c r="M93" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N93" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:14">
+      <x:c r="A94" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="C94" s="1">
+        <x:v>38493</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G94" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="H94" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J94" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K94" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L94" s="2">
+        <x:v>7.92</x:v>
+      </x:c>
+      <x:c r="M94" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N94" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:14">
+      <x:c r="A95" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="C95" s="1">
+        <x:v>38853</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="G95" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="H95" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J95" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K95" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L95" s="2">
+        <x:v>7.16</x:v>
+      </x:c>
+      <x:c r="M95" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N95" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:14">
+      <x:c r="A96" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="C96" s="1">
+        <x:v>38549</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="G96" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="H96" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="J96" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="K96" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L96" s="2">
+        <x:v>4.88</x:v>
+      </x:c>
+      <x:c r="M96" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N96" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:14">
+      <x:c r="A97" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="C97" s="1">
+        <x:v>38763</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="G97" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="H97" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J97" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K97" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L97" s="2">
+        <x:v>7.74</x:v>
+      </x:c>
+      <x:c r="M97" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N97" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:14">
+      <x:c r="A98" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="C98" s="1">
+        <x:v>38573</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="G98" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="H98" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J98" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K98" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L98" s="2">
+        <x:v>8.77</x:v>
+      </x:c>
+      <x:c r="M98" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N98" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:14">
+      <x:c r="A99" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="C99" s="1">
+        <x:v>38895</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G99" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="H99" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="I99" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J99" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K99" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L99" s="2">
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="M99" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N99" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:14">
+      <x:c r="A100" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="C100" s="1">
+        <x:v>38393</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="G100" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="H100" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="I100" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J100" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K100" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L100" s="2">
+        <x:v>7.07</x:v>
+      </x:c>
+      <x:c r="M100" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N100" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:14">
+      <x:c r="A101" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="C101" s="1">
+        <x:v>39305</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E101" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G101" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="H101" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I101" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="J101" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K101" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L101" s="2">
+        <x:v>7.56</x:v>
+      </x:c>
+      <x:c r="M101" s="3">
+        <x:v>46304.6390755903</x:v>
+      </x:c>
+      <x:c r="N101" s="3">
+        <x:v>46304.6390755903</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3615,11 +6761,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B10"/>
+  <x:dimension ref="A1:B29"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="19.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" s="4" customFormat="1">
@@ -3635,7 +6781,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
@@ -3643,7 +6789,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
@@ -3651,55 +6797,543 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:2">
+      <x:c r="A11" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:2">
+      <x:c r="A12" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:2">
+      <x:c r="A13" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:2">
+      <x:c r="A14" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:2">
+      <x:c r="A15" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:2">
+      <x:c r="A16" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:2">
+      <x:c r="A17" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:2">
+      <x:c r="A18" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:2">
+      <x:c r="A19" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:2">
+      <x:c r="A20" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:2">
+      <x:c r="A21" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:2">
+      <x:c r="A22" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:2">
+      <x:c r="A23" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:2">
+      <x:c r="A24" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:2">
+      <x:c r="A25" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:2">
+      <x:c r="A26" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:2">
+      <x:c r="A27" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:2">
+      <x:c r="A28" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:2">
+      <x:c r="A29" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:2">
+      <x:c r="A30" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:2">
+      <x:c r="A31" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:2">
+      <x:c r="A32" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:2">
+      <x:c r="A33" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:2">
+      <x:c r="A34" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:2">
+      <x:c r="A35" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:2">
+      <x:c r="A36" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:2">
+      <x:c r="A37" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:2">
+      <x:c r="A38" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:2">
+      <x:c r="A39" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:2">
+      <x:c r="A40" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:2">
+      <x:c r="A41" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:2">
+      <x:c r="A42" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:2">
+      <x:c r="A43" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:2">
+      <x:c r="A44" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:2">
+      <x:c r="A45" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:2">
+      <x:c r="A46" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:2">
+      <x:c r="A47" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:2">
+      <x:c r="A48" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:2">
+      <x:c r="A49" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:2">
+      <x:c r="A50" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:2">
+      <x:c r="A51" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:2">
+      <x:c r="A52" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:2">
+      <x:c r="A53" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:2">
+      <x:c r="A54" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:2">
+      <x:c r="A55" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:2">
+      <x:c r="A56" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:2">
+      <x:c r="A57" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:2">
+      <x:c r="A58" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:2">
+      <x:c r="A59" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:2">
+      <x:c r="A60" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:2">
+      <x:c r="A61" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:2">
+      <x:c r="A62" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:2">
+      <x:c r="A63" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:2">
+      <x:c r="A64" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:2">
+      <x:c r="A65" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:2">
+      <x:c r="A66" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:2">
+      <x:c r="A67" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>615</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:2">
+      <x:c r="A68" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:2">
+      <x:c r="A69" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>617</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:2">
+      <x:c r="A70" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>618</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:2">
+      <x:c r="A71" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>619</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/src/AVLStudentManagement.App/data/HoSoSinhVien.xlsx
+++ b/src/AVLStudentManagement.App/data/HoSoSinhVien.xlsx
@@ -59,15 +59,39 @@
     <x:t>NgayCapNhat</x:t>
   </x:si>
   <x:si>
+    <x:t>100000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Chí Bảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nam</x:t>
+  </x:si>
+  <x:si>
+    <x:t>087204007867</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dh5200357@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0337778965</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đồng Tháp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22KT1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kinh tế</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DangHoc</x:t>
+  </x:si>
+  <x:si>
     <x:t>12345678</x:t>
   </x:si>
   <x:si>
-    <x:t>Huỳnh Chí Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nam</x:t>
-  </x:si>
-  <x:si>
     <x:t>999999999999</x:t>
   </x:si>
   <x:si>
@@ -86,9 +110,6 @@
     <x:t>Công nghệ thông tin</x:t>
   </x:si>
   <x:si>
-    <x:t>DangHoc</x:t>
-  </x:si>
-  <x:si>
     <x:t>22011001</x:t>
   </x:si>
   <x:si>
@@ -323,12 +344,6 @@
     <x:t>0954458592</x:t>
   </x:si>
   <x:si>
-    <x:t>22KT1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kinh tế</x:t>
-  </x:si>
-  <x:si>
     <x:t>ThoiHoc</x:t>
   </x:si>
   <x:si>
@@ -885,6 +900,15 @@
   </x:si>
   <x:si>
     <x:t>0989472504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22041050</x:t>
+  </x:si>
+  <x:si>
+    <x:t>999999999998</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22041099@student.edu.vn</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1295,10 +1319,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N52"/>
+  <x:dimension ref="A1:N54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="18.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.996339" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="8.282054" style="0" customWidth="1"/>
@@ -1365,7 +1389,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>40095</x:v>
+        <x:v>38124</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>16</x:v>
@@ -1392,13 +1416,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L2" s="2">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M2" s="3">
-        <x:v>46304.380848044</x:v>
+        <x:v>46304.4268097685</x:v>
       </x:c>
       <x:c r="N2" s="3">
-        <x:v>46304.380848044</x:v>
+        <x:v>46304.4268097685</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
@@ -1406,43 +1430,43 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>38168</x:v>
+        <x:v>40095</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="G3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="H3" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
+      <x:c r="I3" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="K3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L3" s="2">
-        <x:v>3.98</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M3" s="3">
-        <x:v>45901.3333333333</x:v>
+        <x:v>46304.380848044</x:v>
       </x:c>
       <x:c r="N3" s="3">
-        <x:v>45901.3333333333</x:v>
+        <x:v>46304.380848044</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
@@ -1453,84 +1477,84 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1">
-        <x:v>38865</x:v>
+        <x:v>38168</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="F4" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="G4" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L4" s="2">
-        <x:v>1.1</x:v>
+        <x:v>3.98</x:v>
       </x:c>
       <x:c r="M4" s="3">
-        <x:v>45901.3527777778</x:v>
+        <x:v>45901.3333333333</x:v>
       </x:c>
       <x:c r="N4" s="3">
-        <x:v>45901.3527777778</x:v>
+        <x:v>45901.3333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:14">
       <x:c r="A5" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C5" s="1">
-        <x:v>38704</x:v>
+        <x:v>38865</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L5" s="2">
-        <x:v>1.44</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="M5" s="3">
-        <x:v>45901.3722222222</x:v>
+        <x:v>45901.3527777778</x:v>
       </x:c>
       <x:c r="N5" s="3">
-        <x:v>45901.3722222222</x:v>
+        <x:v>45901.3527777778</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:14">
@@ -1541,7 +1565,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>38316</x:v>
+        <x:v>38704</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>16</x:v>
@@ -1556,641 +1580,641 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L6" s="2">
-        <x:v>2.09</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="M6" s="3">
-        <x:v>45901.3916666667</x:v>
+        <x:v>45901.3722222222</x:v>
       </x:c>
       <x:c r="N6" s="3">
-        <x:v>45901.3916666667</x:v>
+        <x:v>45901.3722222222</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:14">
       <x:c r="A7" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>38302</x:v>
+        <x:v>38316</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L7" s="2">
-        <x:v>1.6</x:v>
+        <x:v>2.09</x:v>
       </x:c>
       <x:c r="M7" s="3">
-        <x:v>45901.4111111111</x:v>
+        <x:v>45901.3916666667</x:v>
       </x:c>
       <x:c r="N7" s="3">
-        <x:v>45901.4111111111</x:v>
+        <x:v>45901.3916666667</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:14">
       <x:c r="A8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>38003</x:v>
+        <x:v>38302</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L8" s="2">
-        <x:v>3.14</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="M8" s="3">
-        <x:v>45901.4305555556</x:v>
+        <x:v>45901.4111111111</x:v>
       </x:c>
       <x:c r="N8" s="3">
-        <x:v>45901.4305555556</x:v>
+        <x:v>45901.4111111111</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>38333</x:v>
+        <x:v>38003</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="K9" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L9" s="2">
-        <x:v>3.63</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="M9" s="3">
-        <x:v>45901.45</x:v>
+        <x:v>45901.4305555556</x:v>
       </x:c>
       <x:c r="N9" s="3">
-        <x:v>45901.45</x:v>
+        <x:v>45901.4305555556</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>38006</x:v>
+        <x:v>38333</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="K10" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L10" s="2">
-        <x:v>3.78</x:v>
+        <x:v>3.63</x:v>
       </x:c>
       <x:c r="M10" s="3">
-        <x:v>45901.4694444444</x:v>
+        <x:v>45901.45</x:v>
       </x:c>
       <x:c r="N10" s="3">
-        <x:v>45901.4694444444</x:v>
+        <x:v>45901.45</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>38127</x:v>
+        <x:v>38006</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L11" s="2">
-        <x:v>1.99</x:v>
+        <x:v>3.78</x:v>
       </x:c>
       <x:c r="M11" s="3">
-        <x:v>45901.4888888889</x:v>
+        <x:v>45901.4694444444</x:v>
       </x:c>
       <x:c r="N11" s="3">
-        <x:v>45901.4888888889</x:v>
+        <x:v>45901.4694444444</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>38496</x:v>
+        <x:v>38127</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L12" s="2">
-        <x:v>1.7</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="M12" s="3">
-        <x:v>45901.5083333333</x:v>
+        <x:v>45901.4888888889</x:v>
       </x:c>
       <x:c r="N12" s="3">
-        <x:v>45901.5083333333</x:v>
+        <x:v>45901.4888888889</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>38078</x:v>
+        <x:v>38496</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L13" s="2">
-        <x:v>2.67</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="M13" s="3">
-        <x:v>45901.5277777778</x:v>
+        <x:v>45901.5083333333</x:v>
       </x:c>
       <x:c r="N13" s="3">
-        <x:v>45901.5277777778</x:v>
+        <x:v>45901.5083333333</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>38505</x:v>
+        <x:v>38078</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J14" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="K14" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L14" s="2">
-        <x:v>2.34</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="M14" s="3">
-        <x:v>45901.5472222222</x:v>
+        <x:v>45901.5277777778</x:v>
       </x:c>
       <x:c r="N14" s="3">
-        <x:v>45901.5472222222</x:v>
+        <x:v>45901.5277777778</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>38099</x:v>
+        <x:v>38505</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J15" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L15" s="2">
-        <x:v>1.41</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="M15" s="3">
-        <x:v>45901.5666666667</x:v>
+        <x:v>45901.5472222222</x:v>
       </x:c>
       <x:c r="N15" s="3">
-        <x:v>45901.5666666667</x:v>
+        <x:v>45901.5472222222</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:14">
       <x:c r="A16" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>38603</x:v>
+        <x:v>38099</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L16" s="2">
-        <x:v>3.64</x:v>
+        <x:v>1.41</x:v>
       </x:c>
       <x:c r="M16" s="3">
-        <x:v>45901.3381944444</x:v>
+        <x:v>45901.5666666667</x:v>
       </x:c>
       <x:c r="N16" s="3">
-        <x:v>45901.3381944444</x:v>
+        <x:v>45901.5666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:14">
       <x:c r="A17" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
+      <x:c r="C17" s="1">
+        <x:v>38603</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="C17" s="1">
-        <x:v>38430</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
+      <x:c r="F17" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F17" s="0" t="s">
+      <x:c r="G17" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G17" s="0" t="s">
+      <x:c r="H17" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="L17" s="2">
-        <x:v>1.67</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="M17" s="3">
-        <x:v>45901.3576388889</x:v>
+        <x:v>45901.3381944444</x:v>
       </x:c>
       <x:c r="N17" s="3">
-        <x:v>45901.3576388889</x:v>
+        <x:v>45901.3381944444</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:14">
       <x:c r="A18" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="C18" s="1">
+        <x:v>38430</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C18" s="1">
-        <x:v>38053</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
+      <x:c r="F18" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="F18" s="0" t="s">
+      <x:c r="G18" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L18" s="2">
-        <x:v>2.7</x:v>
+        <x:v>1.67</x:v>
       </x:c>
       <x:c r="M18" s="3">
-        <x:v>45901.3770833333</x:v>
+        <x:v>45901.3576388889</x:v>
       </x:c>
       <x:c r="N18" s="3">
-        <x:v>45901.3770833333</x:v>
+        <x:v>45901.3576388889</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:14">
       <x:c r="A19" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>38720</x:v>
+        <x:v>38053</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L19" s="2">
-        <x:v>2.12</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="M19" s="3">
-        <x:v>45901.3965277778</x:v>
+        <x:v>45901.3770833333</x:v>
       </x:c>
       <x:c r="N19" s="3">
-        <x:v>45901.3965277778</x:v>
+        <x:v>45901.3770833333</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:14">
       <x:c r="A20" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B20" s="0" t="s">
+      <x:c r="C20" s="1">
+        <x:v>38720</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C20" s="1">
-        <x:v>38808</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
+      <x:c r="F20" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F20" s="0" t="s">
+      <x:c r="G20" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G20" s="0" t="s">
+      <x:c r="H20" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H20" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L20" s="2">
-        <x:v>1.22</x:v>
+        <x:v>2.12</x:v>
       </x:c>
       <x:c r="M20" s="3">
-        <x:v>45901.4159722222</x:v>
+        <x:v>45901.3965277778</x:v>
       </x:c>
       <x:c r="N20" s="3">
-        <x:v>45901.4159722222</x:v>
+        <x:v>45901.3965277778</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:14">
@@ -2201,10 +2225,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>38307</x:v>
+        <x:v>38808</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>128</x:v>
@@ -2216,25 +2240,25 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L21" s="2">
-        <x:v>3.21</x:v>
+        <x:v>1.22</x:v>
       </x:c>
       <x:c r="M21" s="3">
-        <x:v>45901.4354166667</x:v>
+        <x:v>45901.4159722222</x:v>
       </x:c>
       <x:c r="N21" s="3">
-        <x:v>45901.4354166667</x:v>
+        <x:v>45901.4159722222</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:14">
@@ -2245,10 +2269,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>38446</x:v>
+        <x:v>38307</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>133</x:v>
@@ -2260,25 +2284,25 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L22" s="2">
-        <x:v>2.96</x:v>
+        <x:v>3.21</x:v>
       </x:c>
       <x:c r="M22" s="3">
-        <x:v>45901.4548611111</x:v>
+        <x:v>45901.4354166667</x:v>
       </x:c>
       <x:c r="N22" s="3">
-        <x:v>45901.4548611111</x:v>
+        <x:v>45901.4354166667</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:14">
@@ -2289,10 +2313,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>38757</x:v>
+        <x:v>38446</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>138</x:v>
@@ -2304,25 +2328,25 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L23" s="2">
-        <x:v>3.29</x:v>
+        <x:v>2.96</x:v>
       </x:c>
       <x:c r="M23" s="3">
-        <x:v>45901.4743055556</x:v>
+        <x:v>45901.4548611111</x:v>
       </x:c>
       <x:c r="N23" s="3">
-        <x:v>45901.4743055556</x:v>
+        <x:v>45901.4548611111</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:14">
@@ -2333,10 +2357,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>38143</x:v>
+        <x:v>38757</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
         <x:v>143</x:v>
@@ -2348,25 +2372,25 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L24" s="2">
-        <x:v>1.52</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="M24" s="3">
-        <x:v>45901.49375</x:v>
+        <x:v>45901.4743055556</x:v>
       </x:c>
       <x:c r="N24" s="3">
-        <x:v>45901.49375</x:v>
+        <x:v>45901.4743055556</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:14">
@@ -2377,7 +2401,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>38162</x:v>
+        <x:v>38143</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>16</x:v>
@@ -2392,25 +2416,25 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L25" s="2">
-        <x:v>2.55</x:v>
+        <x:v>1.52</x:v>
       </x:c>
       <x:c r="M25" s="3">
-        <x:v>45901.5131944444</x:v>
+        <x:v>45901.49375</x:v>
       </x:c>
       <x:c r="N25" s="3">
-        <x:v>45901.5131944444</x:v>
+        <x:v>45901.49375</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:14">
@@ -2421,7 +2445,7 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>38785</x:v>
+        <x:v>38162</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>16</x:v>
@@ -2436,25 +2460,25 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L26" s="2">
-        <x:v>3.03</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="M26" s="3">
-        <x:v>45901.5326388889</x:v>
+        <x:v>45901.5131944444</x:v>
       </x:c>
       <x:c r="N26" s="3">
-        <x:v>45901.5326388889</x:v>
+        <x:v>45901.5131944444</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:14">
@@ -2465,7 +2489,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>38112</x:v>
+        <x:v>38785</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>16</x:v>
@@ -2477,72 +2501,72 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="L27" s="2">
-        <x:v>2.51</x:v>
+        <x:v>3.03</x:v>
       </x:c>
       <x:c r="M27" s="3">
-        <x:v>45901.5520833333</x:v>
+        <x:v>45901.5326388889</x:v>
       </x:c>
       <x:c r="N27" s="3">
-        <x:v>45901.5520833333</x:v>
+        <x:v>45901.5326388889</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:14">
       <x:c r="A28" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>38246</x:v>
+        <x:v>38112</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H28" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L28" s="2">
-        <x:v>3.26</x:v>
+        <x:v>2.51</x:v>
       </x:c>
       <x:c r="M28" s="3">
-        <x:v>45901.5715277778</x:v>
+        <x:v>45901.5520833333</x:v>
       </x:c>
       <x:c r="N28" s="3">
-        <x:v>45901.5715277778</x:v>
+        <x:v>45901.5520833333</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:14">
@@ -2553,7 +2577,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>38849</x:v>
+        <x:v>38246</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>16</x:v>
@@ -2568,157 +2592,157 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L29" s="2">
-        <x:v>3.56</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="M29" s="3">
-        <x:v>45901.3430555556</x:v>
+        <x:v>45901.5715277778</x:v>
       </x:c>
       <x:c r="N29" s="3">
-        <x:v>45901.3430555556</x:v>
+        <x:v>45901.5715277778</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:14">
       <x:c r="A30" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C30" s="1">
+        <x:v>38849</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B30" s="0" t="s">
+      <x:c r="F30" s="0" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="C30" s="1">
-        <x:v>38209</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E30" s="0" t="s">
+      <x:c r="G30" s="0" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="F30" s="0" t="s">
+      <x:c r="H30" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G30" s="0" t="s">
+      <x:c r="J30" s="0" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="H30" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="I30" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="J30" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
       <x:c r="K30" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L30" s="2">
-        <x:v>2.71</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="M30" s="3">
-        <x:v>45901.3625</x:v>
+        <x:v>45901.3430555556</x:v>
       </x:c>
       <x:c r="N30" s="3">
-        <x:v>45901.3625</x:v>
+        <x:v>45901.3430555556</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:14">
       <x:c r="A31" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="B31" s="0" t="s">
+      <x:c r="C31" s="1">
+        <x:v>38209</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="C31" s="1">
-        <x:v>38479</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E31" s="0" t="s">
+      <x:c r="F31" s="0" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="F31" s="0" t="s">
+      <x:c r="G31" s="0" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="G31" s="0" t="s">
+      <x:c r="H31" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="H31" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I31" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L31" s="2">
-        <x:v>1.93</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="M31" s="3">
-        <x:v>45901.3819444444</x:v>
+        <x:v>45901.3625</x:v>
       </x:c>
       <x:c r="N31" s="3">
-        <x:v>45901.3819444444</x:v>
+        <x:v>45901.3625</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:14">
       <x:c r="A32" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
       <x:c r="C32" s="1">
-        <x:v>38359</x:v>
+        <x:v>38479</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="F32" s="0" t="s">
+      <x:c r="G32" s="0" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="G32" s="0" t="s">
+      <x:c r="H32" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="H32" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="I32" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="J32" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="K32" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="L32" s="2">
-        <x:v>2.04</x:v>
+        <x:v>1.93</x:v>
       </x:c>
       <x:c r="M32" s="3">
-        <x:v>45901.4013888889</x:v>
+        <x:v>45901.3819444444</x:v>
       </x:c>
       <x:c r="N32" s="3">
-        <x:v>45901.4013888889</x:v>
+        <x:v>45901.3819444444</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:14">
@@ -2729,7 +2753,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>38535</x:v>
+        <x:v>38359</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>16</x:v>
@@ -2741,72 +2765,72 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L33" s="2">
-        <x:v>3.36</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="M33" s="3">
-        <x:v>45901.4208333333</x:v>
+        <x:v>45901.4013888889</x:v>
       </x:c>
       <x:c r="N33" s="3">
-        <x:v>45901.4208333333</x:v>
+        <x:v>45901.4013888889</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:14">
       <x:c r="A34" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>38131</x:v>
+        <x:v>38535</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L34" s="2">
-        <x:v>2.92</x:v>
+        <x:v>3.36</x:v>
       </x:c>
       <x:c r="M34" s="3">
-        <x:v>45901.4402777778</x:v>
+        <x:v>45901.4208333333</x:v>
       </x:c>
       <x:c r="N34" s="3">
-        <x:v>45901.4402777778</x:v>
+        <x:v>45901.4208333333</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:14">
@@ -2817,10 +2841,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>38167</x:v>
+        <x:v>38131</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
         <x:v>200</x:v>
@@ -2832,25 +2856,25 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="2">
-        <x:v>2.42</x:v>
+        <x:v>2.92</x:v>
       </x:c>
       <x:c r="M35" s="3">
-        <x:v>45901.4597222222</x:v>
+        <x:v>45901.4402777778</x:v>
       </x:c>
       <x:c r="N35" s="3">
-        <x:v>45901.4597222222</x:v>
+        <x:v>45901.4402777778</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:14">
@@ -2861,10 +2885,10 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>37994</x:v>
+        <x:v>38167</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
         <x:v>205</x:v>
@@ -2876,25 +2900,25 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L36" s="2">
-        <x:v>2.9</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="M36" s="3">
-        <x:v>45901.4791666667</x:v>
+        <x:v>45901.4597222222</x:v>
       </x:c>
       <x:c r="N36" s="3">
-        <x:v>45901.4791666667</x:v>
+        <x:v>45901.4597222222</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:14">
@@ -2905,10 +2929,10 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>38877</x:v>
+        <x:v>37994</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
         <x:v>210</x:v>
@@ -2920,25 +2944,25 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L37" s="2">
-        <x:v>3.58</x:v>
+        <x:v>2.9</x:v>
       </x:c>
       <x:c r="M37" s="3">
-        <x:v>45901.4986111111</x:v>
+        <x:v>45901.4791666667</x:v>
       </x:c>
       <x:c r="N37" s="3">
-        <x:v>45901.4986111111</x:v>
+        <x:v>45901.4791666667</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:14">
@@ -2949,10 +2973,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>38247</x:v>
+        <x:v>38877</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
         <x:v>215</x:v>
@@ -2964,25 +2988,25 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L38" s="2">
-        <x:v>1.61</x:v>
+        <x:v>3.58</x:v>
       </x:c>
       <x:c r="M38" s="3">
-        <x:v>45901.5180555556</x:v>
+        <x:v>45901.4986111111</x:v>
       </x:c>
       <x:c r="N38" s="3">
-        <x:v>45901.5180555556</x:v>
+        <x:v>45901.4986111111</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:14">
@@ -2993,10 +3017,10 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>38592</x:v>
+        <x:v>38247</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
         <x:v>220</x:v>
@@ -3008,25 +3032,25 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I39" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L39" s="2">
-        <x:v>3</x:v>
+        <x:v>1.61</x:v>
       </x:c>
       <x:c r="M39" s="3">
-        <x:v>45901.5375</x:v>
+        <x:v>45901.5180555556</x:v>
       </x:c>
       <x:c r="N39" s="3">
-        <x:v>45901.5375</x:v>
+        <x:v>45901.5180555556</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:14">
@@ -3037,10 +3061,10 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>38310</x:v>
+        <x:v>38592</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
         <x:v>225</x:v>
@@ -3052,25 +3076,25 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L40" s="2">
-        <x:v>3.79</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M40" s="3">
-        <x:v>45901.5569444444</x:v>
+        <x:v>45901.5375</x:v>
       </x:c>
       <x:c r="N40" s="3">
-        <x:v>45901.5569444444</x:v>
+        <x:v>45901.5375</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:14">
@@ -3081,7 +3105,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>38361</x:v>
+        <x:v>38310</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>16</x:v>
@@ -3096,69 +3120,69 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L41" s="2">
-        <x:v>3.15</x:v>
+        <x:v>3.79</x:v>
       </x:c>
       <x:c r="M41" s="3">
-        <x:v>45901.3479166667</x:v>
+        <x:v>45901.5569444444</x:v>
       </x:c>
       <x:c r="N41" s="3">
-        <x:v>45901.3479166667</x:v>
+        <x:v>45901.5569444444</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:14">
       <x:c r="A42" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>38686</x:v>
+        <x:v>38361</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="F42" s="0" t="s">
+      <x:c r="H42" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G42" s="0" t="s">
+      <x:c r="J42" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H42" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I42" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="J42" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
       <x:c r="K42" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L42" s="2">
-        <x:v>2.64</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="M42" s="3">
-        <x:v>45901.3673611111</x:v>
+        <x:v>45901.3479166667</x:v>
       </x:c>
       <x:c r="N42" s="3">
-        <x:v>45901.3673611111</x:v>
+        <x:v>45901.3479166667</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:14">
@@ -3169,7 +3193,7 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>38115</x:v>
+        <x:v>38686</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>16</x:v>
@@ -3184,25 +3208,25 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L43" s="2">
-        <x:v>1.16</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="M43" s="3">
-        <x:v>45901.3868055556</x:v>
+        <x:v>45901.3673611111</x:v>
       </x:c>
       <x:c r="N43" s="3">
-        <x:v>45901.3868055556</x:v>
+        <x:v>45901.3673611111</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:14">
@@ -3213,7 +3237,7 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>38663</x:v>
+        <x:v>38115</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>16</x:v>
@@ -3228,25 +3252,25 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L44" s="2">
-        <x:v>1.14</x:v>
+        <x:v>1.16</x:v>
       </x:c>
       <x:c r="M44" s="3">
-        <x:v>45901.40625</x:v>
+        <x:v>45901.3868055556</x:v>
       </x:c>
       <x:c r="N44" s="3">
-        <x:v>45901.40625</x:v>
+        <x:v>45901.3868055556</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:14">
@@ -3257,10 +3281,10 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>38519</x:v>
+        <x:v>38663</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>252</x:v>
@@ -3272,25 +3296,25 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I45" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L45" s="2">
-        <x:v>2.17</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="M45" s="3">
-        <x:v>45901.4256944444</x:v>
+        <x:v>45901.40625</x:v>
       </x:c>
       <x:c r="N45" s="3">
-        <x:v>45901.4256944444</x:v>
+        <x:v>45901.40625</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:14">
@@ -3301,10 +3325,10 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>38216</x:v>
+        <x:v>38519</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>257</x:v>
@@ -3316,25 +3340,25 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L46" s="2">
-        <x:v>1.4</x:v>
+        <x:v>2.17</x:v>
       </x:c>
       <x:c r="M46" s="3">
-        <x:v>45901.4451388889</x:v>
+        <x:v>45901.4256944444</x:v>
       </x:c>
       <x:c r="N46" s="3">
-        <x:v>45901.4451388889</x:v>
+        <x:v>45901.4256944444</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:14">
@@ -3345,10 +3369,10 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>38690</x:v>
+        <x:v>38216</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>262</x:v>
@@ -3357,116 +3381,116 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L47" s="2">
-        <x:v>3.75</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="M47" s="3">
-        <x:v>45901.4645833333</x:v>
+        <x:v>45901.4451388889</x:v>
       </x:c>
       <x:c r="N47" s="3">
-        <x:v>45901.4645833333</x:v>
+        <x:v>45901.4451388889</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:14">
       <x:c r="A48" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>38721</x:v>
+        <x:v>38690</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L48" s="2">
-        <x:v>3.99</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="M48" s="3">
-        <x:v>45901.4840277778</x:v>
+        <x:v>45901.4645833333</x:v>
       </x:c>
       <x:c r="N48" s="3">
-        <x:v>45901.4840277778</x:v>
+        <x:v>45901.4645833333</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:14">
       <x:c r="A49" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
+      <x:c r="C49" s="1">
+        <x:v>38721</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="C49" s="1">
-        <x:v>38846</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
+      <x:c r="F49" s="0" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="F49" s="0" t="s">
+      <x:c r="G49" s="0" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="G49" s="0" t="s">
+      <x:c r="H49" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="H49" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I49" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L49" s="2">
-        <x:v>2.24</x:v>
+        <x:v>3.99</x:v>
       </x:c>
       <x:c r="M49" s="3">
-        <x:v>45901.5034722222</x:v>
+        <x:v>45901.4840277778</x:v>
       </x:c>
       <x:c r="N49" s="3">
-        <x:v>45901.5034722222</x:v>
+        <x:v>45901.4840277778</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:14">
@@ -3477,10 +3501,10 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>38475</x:v>
+        <x:v>38846</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>277</x:v>
@@ -3492,25 +3516,25 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I50" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J50" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="L50" s="2">
-        <x:v>1.56</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="M50" s="3">
-        <x:v>45901.5229166667</x:v>
+        <x:v>45901.5034722222</x:v>
       </x:c>
       <x:c r="N50" s="3">
-        <x:v>45901.5229166667</x:v>
+        <x:v>45901.5034722222</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:14">
@@ -3521,10 +3545,10 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>38563</x:v>
+        <x:v>38475</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>282</x:v>
@@ -3536,25 +3560,25 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="J51" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L51" s="2">
-        <x:v>1.28</x:v>
+        <x:v>1.56</x:v>
       </x:c>
       <x:c r="M51" s="3">
-        <x:v>45901.5423611111</x:v>
+        <x:v>45901.5229166667</x:v>
       </x:c>
       <x:c r="N51" s="3">
-        <x:v>45901.5423611111</x:v>
+        <x:v>45901.5229166667</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:14">
@@ -3565,10 +3589,10 @@
         <x:v>286</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>38620</x:v>
+        <x:v>38563</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>287</x:v>
@@ -3580,25 +3604,113 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I52" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J52" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L52" s="2">
+        <x:v>1.28</x:v>
+      </x:c>
+      <x:c r="M52" s="3">
+        <x:v>45901.5423611111</x:v>
+      </x:c>
+      <x:c r="N52" s="3">
+        <x:v>45901.5423611111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:14">
+      <x:c r="A53" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C53" s="1">
+        <x:v>38620</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E53" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J53" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K53" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L53" s="2">
         <x:v>3.8</x:v>
       </x:c>
-      <x:c r="M52" s="3">
+      <x:c r="M53" s="3">
         <x:v>45901.5618055556</x:v>
       </x:c>
-      <x:c r="N52" s="3">
+      <x:c r="N53" s="3">
         <x:v>45901.5618055556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:14">
+      <x:c r="A54" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C54" s="1">
+        <x:v>38620</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E54" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J54" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K54" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L54" s="2">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="M54" s="3">
+        <x:v>46304.4169022454</x:v>
+      </x:c>
+      <x:c r="N54" s="3">
+        <x:v>46304.4169022454</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3632,74 +3744,74 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/src/AVLStudentManagement.App/data/HoSoSinhVien.xlsx
+++ b/src/AVLStudentManagement.App/data/HoSoSinhVien.xlsx
@@ -59,15 +59,237 @@
     <x:t>NgayCapNhat</x:t>
   </x:si>
   <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Thu Tú</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nữ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086307885833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tubt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0791553778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 2, Thành phố Vĩnh Long, Tỉnh Vĩnh Long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Kinh tế</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đang học</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Thanh Bảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nam</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206462993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baont@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0917102655</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Chợ, Xã Bình Phú, Huyện Càng Long, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Cẩm Trang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095305101433</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tranghc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0933093670</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 3, Thành phố Bạc Liêu, Tỉnh Bạc Liêu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Kỹ thuật và Công nghệ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Ngọc Thảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307468467</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaohn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0944797658</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Ba Se, Xã Châu Điền, Huyện Cầu Kè, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Y Dược</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Thanh Nhi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307573543</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhitt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0900911131</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Sóc Xoài, Xã Mỹ Long Bắc, Huyện Cầu Ngang, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25NNB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Ngoại ngữ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Mỹ Trâm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092305585490</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tramdm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323541573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường An Khánh, Quận Ninh Kiều, Thành phố Cần Thơ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Quốc Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>096207549655</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duydq@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0901928766</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 9, Thành phố Cà Mau, Tỉnh Cà Mau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Sư phạm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thôi học</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Ngọc Duyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094306526218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyentn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0919559096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 5, Thị xã Vĩnh Châu, Tỉnh Sóc Trăng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25SPB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Hồng Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094305029747</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanth@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0351950522</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Thu Duyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306506337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyenlt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0326320632</x:t>
+  </x:si>
+  <x:si>
     <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>Huỳnh Trọng Long</x:t>
   </x:si>
   <x:si>
-    <x:t>Nam</x:t>
-  </x:si>
-  <x:si>
     <x:t>089207842301</x:t>
   </x:si>
   <x:si>
@@ -83,1762 +305,1543 @@
     <x:t>DA25TTB</x:t>
   </x:si>
   <x:si>
-    <x:t>Trường Kỹ thuật và Công nghệ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đang học</x:t>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Thanh Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307183024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vypt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0977866596</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khóm 2, Phường 7, Thành phố Trà Vinh, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Nông nghiệp - Thủy sản</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Thị Sô Ka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306519287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kalts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0356284533</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khóm 4, Phường 3, Thành phố Trà Vinh, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Khoa Ngôn ngữ, Văn hóa, Nghệ thuật Khmer Nam Bộ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Danh Thị Sô Phia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306635880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phiadts2@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0985002508</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Mỹ Cẩm, Xã Mỹ Cẩm, Huyện Càng Long, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306635388</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phiadts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0763503120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Văn Thịnh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205351969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thinhvv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0320618527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NNB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Nhật Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094207436366</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyvn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0948971062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Hòa Thành, Xã Hòa Tú, Huyện Mỹ Xuyên, Tỉnh Sóc Trăng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mai Thị Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095306065910</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanmt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0914216394</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Minh Bảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205625244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baohm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0970440837</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Nhị Trường, Xã Nhị Trường, Huyện Cầu Ngang, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Bích Nhung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305174514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhunglb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0703121935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Hiếu Trung, Xã Hiếu Tử, Huyện Tiểu Cần, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sơn Thị Sô Ka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305867970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kasts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0918529360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nguyễn Kim Tú</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307660952</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tunk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0942808460</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Ngãi Xuyên, Xã Ngãi Xuyên, Huyện Trà Cú, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Kim Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305525236</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanpk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0381915053</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Thanh Phát</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094207922237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phattt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0984724383</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Danh Vi Rây</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206051573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raydv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0976231518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đỗ Bích Nhung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306230754</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhungdb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0705573756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Yến Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307606855</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maity@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0763776371</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Bích Ngọc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>083307860204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ngoctb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0354270093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp An Hội, Xã An Hóa, Huyện Châu Thành, Tỉnh Bến Tre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Thị Ngọc Thu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092306333499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thuctn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0909492010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Vi Rây</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207043792</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raycv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0326151026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Kim Phượng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306558147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuonglk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0945858133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thạch Hoàng Pha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206168967</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phath@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0764199317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Thị Trâm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305170110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tramtt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0946583809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Tập Ngãi, Xã Tập Ngãi, Huyện Tiểu Cần, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đỗ Ngọc Nhi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094306888995</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhidn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0941476650</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Hoàng Trung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206245323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trungch@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0794333756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Cây Xoài, Xã Hòa Ân, Huyện Cầu Kè, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mai Diễm Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095306682900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maimd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0705377769</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Thanh Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306908861</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nganvt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0324951108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Thị Sa Rây</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306660163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raycts@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0705596382</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Long Hậu, Xã Long Vĩnh, Huyện Duyên Hải, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Thu Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306459796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vyht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0934469754</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phạm Thu Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306115440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nganpt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0385117673</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Trọng Hiếu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205501111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hieuht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0383329486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ngô Mỹ Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094307230815</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongnm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0768848324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Đức Bảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205079152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baohd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0935166077</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bảo lưu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phạm Hoàng Tài</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206869893</x:t>
+  </x:si>
+  <x:si>
+    <x:t>taiph@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0986334014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ngô Công Phước</x:t>
+  </x:si>
+  <x:si>
+    <x:t>083206515146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuocnc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323792853</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA25KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Trọng Hậu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205460345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hautt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0706674128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Sóc Ruộng, Xã Đa Lộc, Huyện Châu Thành, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hồ Phương Lan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307591487</x:t>
+  </x:si>
+  <x:si>
+    <x:t>lanhp@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0948577595</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cao Kim Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089306828375</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maick@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0933961878</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Gia Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206127305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duytg@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0987988924</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Bà Mi, Xã Tập Sơn, Huyện Trà Cú, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Quốc Huy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207457636</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huybq@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0358478239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Mỹ Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086306551414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongpm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0321101268</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Thu Tú</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086306508948</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tudt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0383495362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Yến Trâm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086307418213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tramcy@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0980140725</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ấp Phú Hòa, Xã Phú Thịnh, Huyện Tam Bình, Tỉnh Vĩnh Long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Hồng Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092307615754</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongdh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0989209082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Bích Thảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086305375926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaolb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0387106113</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Cẩm Nhung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307782381</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhunglc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0760121877</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Yến Châu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306402430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>chauhy@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323346251</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Công Thiện</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092205639988</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thienlc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0981384507</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cao Ngọc Như</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095305413982</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhucn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0355398125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Thanh Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089305263995</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongtt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0767796963</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phạm Thị Thảo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306296531</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaopt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0794492684</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Diễm Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306158182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maidd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0324016802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24SPB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Anh Trung</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205242230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trungta@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0948157871</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA24NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Gia Duy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207337323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duypg@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0972945557</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sơn Rô Tha Na</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205905600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nasrt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0767410798</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Đức Lộc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206957866</x:t>
+  </x:si>
+  <x:si>
+    <x:t>locpd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0323569423</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tạ Phương Châu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089305962940</x:t>
+  </x:si>
+  <x:si>
+    <x:t>chautp@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0350865639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Thu Ngọc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092306547883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ngocht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0971261486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Công Khang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>095207717245</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khanglc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0765543972</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Minh Hậu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207587156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>haulm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0385793464</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Hoàng Phát</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086207501341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phatdh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0328273063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Hoàng Phát</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205202547</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phatlh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0386734039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Thúy Phượng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307050145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuongdt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0906637509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Tuấn Lộc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205137234</x:t>
+  </x:si>
+  <x:si>
+    <x:t>locht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0766112392</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Công Thịnh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089205337071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thinhdc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0980653344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sơn Sa Ruôl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084205786003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ruolss@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0768832759</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Anh Kiệt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206511902</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kietba@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0765481323</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thạch Thị Ngọc Thu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>094306995326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thuttn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0911819945</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lâm Hồng Phượng</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092307427774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>phuonglh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0794470273</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Huỳnh Thanh Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084305057488</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nganht@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0973442955</x:t>
+  </x:si>
+  <x:si>
+    <x:t>81</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Võ Minh Lộc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>087206547340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>locvm@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0906634998</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 1, Thành phố Cao Lãnh, Tỉnh Đồng Tháp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cao Gia Nghĩa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086205850671</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nghiacg@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0761473048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Hồng Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089306187368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vyth@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0972288261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Cẩm Vy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>091305458272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>vydc@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0911557161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường Vĩnh Thanh, Thành phố Rạch Giá, Tỉnh Kiên Giang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Diễm Hương</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306708343</x:t>
+  </x:si>
+  <x:si>
+    <x:t>huongtd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0799434505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phan Thanh Thiện</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084207500796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thienpt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0327731674</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Châu Diễm Ngân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>092305851812</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ngancd@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0768437124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mai Thanh Hân</x:t>
+  </x:si>
+  <x:si>
+    <x:t>091307189570</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanmt2@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0704376698</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ngô Anh Thiện</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206136968</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thienna@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0905452018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Nhật Long</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084206810306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>longbn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0708690541</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lý Bích Duyên</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307188888</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyenlb@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0907667529</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Đặng Tuấn Hiếu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>091205406217</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hieudt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0351779197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Yến Linh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>089306185755</x:t>
+  </x:si>
+  <x:si>
+    <x:t>linhdy@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0704865793</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bùi Ngọc Như</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306591393</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhubn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0976364796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Kim Nhi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>087306305906</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nhidk@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0978064729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trương Ngọc Trang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084307681088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>trangtn@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0935679527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dương Hoàng Mai</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084306869299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maidh@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0927530256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phường 1, Thành phố Trà Vinh, Tỉnh Trà Vinh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>96</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lê Ngọc An</x:t>
+  </x:si>
+  <x:si>
+    <x:t>086307111356</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anln@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0933356573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trần Thanh Bình</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084300803463</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bìnhtt@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0918784870</x:t>
   </x:si>
   <x:si>
     <x:t>98</x:t>
   </x:si>
   <x:si>
-    <x:t>Võ Thu Ngọc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nữ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086307136141</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ngocvt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0321527788</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Phú Hòa, Xã Phú Thịnh, Huyện Tam Bình, Tỉnh Vĩnh Long</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25YDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trường Y Dược</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Danh Vi Rây</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206051573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raydv@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0976231518</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Khóm 4, Phường 3, Thành phố Trà Vinh, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24KMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Khoa Ngôn ngữ Khmer Nam Bộ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Thanh Nhi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307573543</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhitt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0900911131</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Sóc Xoài, Xã Mỹ Long Bắc, Huyện Cầu Ngang, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25NNB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Khoa Ngoại ngữ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Thanh Hương</x:t>
-  </x:si>
-  <x:si>
-    <x:t>089305263995</x:t>
-  </x:si>
-  <x:si>
-    <x:t>huongtt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0767796963</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24TTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Trọng Hậu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205460345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hautt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0706674128</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Sóc Ruộng, Xã Đa Lộc, Huyện Châu Thành, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24YDB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cao Gia Nghĩa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086205850671</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nghiacg@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0761473048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phạm Thị Thảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306296531</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thaopt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0794492684</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Long Hậu, Xã Long Vĩnh, Huyện Duyên Hải, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lâm Thu Duyên</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306506337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duyenlt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0326320632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Ba Se, Xã Châu Điền, Huyện Cầu Kè, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24TTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nguyễn Kim Tú</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307660952</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tunk@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0942808460</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Ngãi Xuyên, Xã Ngãi Xuyên, Huyện Trà Cú, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25NHB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Khoa Nông nghiệp - Thủy sản</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Minh Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205625244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>baohm@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0970440837</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Nhị Trường, Xã Nhị Trường, Huyện Cầu Ngang, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24KTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trường Kinh tế, Luật</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Châu Thị Sa Rây</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306660163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raycts@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0705596382</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24KMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Thu Tú</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086306508948</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tudt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0383495362</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phường 2, Thành phố Vĩnh Long, Tỉnh Vĩnh Long</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Danh Thị Sô Phia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306635388</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phiadts@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0763503120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Mỹ Cẩm, Xã Mỹ Cẩm, Huyện Càng Long, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25KMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Hồng Vy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>089306187368</x:t>
-  </x:si>
-  <x:si>
-    <x:t>vyth@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0972288261</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24KTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bảo lưu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Châu Thị Ngọc Thu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>092306333499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thuctn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0909492010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phường An Khánh, Quận Ninh Kiều, Thành phố Cần Thơ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Anh Kiệt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206511902</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kietba@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0765481323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24SPB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trường Sư phạm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Cẩm Nhung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307782381</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhunglc@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0760121877</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25TTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lý Bích Duyên</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307188888</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duyenlb@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0907667529</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Tập Ngãi, Xã Tập Ngãi, Huyện Tiểu Cần, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25NHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Đức Lộc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206957866</x:t>
-  </x:si>
-  <x:si>
-    <x:t>locpd@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0323569423</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Chợ, Xã Bình Phú, Huyện Càng Long, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Yến Linh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>089306185755</x:t>
-  </x:si>
-  <x:si>
-    <x:t>linhdy@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0704865793</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24NNB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Văn Hiếu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084207028723</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hieuhv@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0708513006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25SPB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Cẩm Trang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>095305101433</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tranghc@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0933093670</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phường 3, Thành phố Bạc Liêu, Tỉnh Bạc Liêu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Châu Hoàng Trung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206245323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>trungch@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0794333756</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Cây Xoài, Xã Hòa Ân, Huyện Cầu Kè, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24SPA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Mỹ Trâm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>092305585490</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tramdm@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0323541573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24NNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Văn Thịnh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205351969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thinhvv@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0320618527</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Khóm 2, Phường 7, Thành phố Trà Vinh, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Cẩm Vy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>091305458272</x:t>
-  </x:si>
-  <x:si>
-    <x:t>vydc@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0911557161</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phường Vĩnh Thanh, Thành phố Rạch Giá, Tỉnh Kiên Giang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24NHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Ngọc Trang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307681088</x:t>
-  </x:si>
-  <x:si>
-    <x:t>trangtn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0935679527</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ngô Công Phước</x:t>
-  </x:si>
-  <x:si>
-    <x:t>083206515146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phuocnc@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0323792853</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp An Hội, Xã An Hóa, Huyện Châu Thành, Tỉnh Bến Tre</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25KTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Thu Ngọc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>092306547883</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ngocht@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0971261486</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thôi học</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hồ Ngọc Thảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307468467</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thaohn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0944797658</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Kim Hân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084305525236</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hanpk@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0381915053</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Tuấn Lộc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205137234</x:t>
-  </x:si>
-  <x:si>
-    <x:t>locht@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0766112392</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24NHB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Thanh Ngân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084305057488</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nganht@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0973442955</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lâm Hồng Phượng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>092307427774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phuonglh@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0794470273</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25KTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mai Thị Hân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>095306065910</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hanmt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0914216394</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Thanh Thiện</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084207500796</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thienpt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0327731674</x:t>
-  </x:si>
-  <x:si>
-    <x:t>49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Gia Duy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206127305</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duytg@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0987988924</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Bà Mi, Xã Tập Sơn, Huyện Trà Cú, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thạch Hoàng Pha</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206168967</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phath@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0764199317</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Thanh Ngân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306908861</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nganvt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0324951108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Huỳnh Yến Châu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306402430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>chauhy@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0323346251</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25YDB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thạch Thị Ngọc Thu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>094306995326</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thuttn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0911819945</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phường 5, Thị xã Vĩnh Châu, Tỉnh Sóc Trăng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Ngọc Duyên</x:t>
-  </x:si>
-  <x:si>
-    <x:t>094306526218</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duyentn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0919559096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lý Minh Hậu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084207587156</x:t>
-  </x:si>
-  <x:si>
-    <x:t>haulm@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0385793464</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lý Hoàng Phát</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205202547</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phatlh@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0386734039</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Kim Nhi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>087306305906</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhidk@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0978064729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phường 1, Thành phố Cao Lãnh, Tỉnh Đồng Tháp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trần Yến Mai</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307606855</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maity@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0763776371</x:t>
-  </x:si>
-  <x:si>
-    <x:t>39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hồ Thu Vy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306459796</x:t>
-  </x:si>
-  <x:si>
-    <x:t>vyht@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0934469754</x:t>
-  </x:si>
-  <x:si>
-    <x:t>63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trần Anh Trung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205242230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>trungta@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0948157871</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Công Thịnh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>089205337071</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thinhdc@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0980653344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Thúy Phượng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307050145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phuongdt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0906637509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tạ Hồng Hân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>094305029747</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hanth@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0351950522</x:t>
-  </x:si>
-  <x:si>
-    <x:t>62</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Diễm Mai</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306158182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maidd@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0324016802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Hồng Phượng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084305222815</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phuongvh@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0385522581</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Nhật Duy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>094207436366</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duyvn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0948971062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Hòa Thành, Xã Hòa Tú, Huyện Mỹ Xuyên, Tỉnh Sóc Trăng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Quốc Duy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>096207549655</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duydq@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0901928766</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phường 9, Thành phố Cà Mau, Tỉnh Cà Mau</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25SPA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Thanh Phát</x:t>
-  </x:si>
-  <x:si>
-    <x:t>094207922237</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phattt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0984724383</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ngô Mỹ Hương</x:t>
-  </x:si>
-  <x:si>
-    <x:t>094307230815</x:t>
-  </x:si>
-  <x:si>
-    <x:t>huongnm@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0768848324</x:t>
-  </x:si>
-  <x:si>
-    <x:t>54</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dương Hồng Hương</x:t>
-  </x:si>
-  <x:si>
-    <x:t>092307615754</x:t>
-  </x:si>
-  <x:si>
-    <x:t>huongdh@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0989209082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Thu Tú</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086307885833</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tubt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0791553778</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Tuấn Hiếu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>091205406217</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hieudt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0351779197</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lâm Bích Thảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086305375926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thaolb@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0387106113</x:t>
-  </x:si>
-  <x:si>
-    <x:t>96</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lâm Anh Long</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206223477</x:t>
-  </x:si>
-  <x:si>
-    <x:t>longla@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0937337507</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Kim Phượng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306558147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phuonglk@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0945858133</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA24YDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hồ Đức Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205079152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>baohd@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0935166077</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Ngọc Như</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306591393</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhubn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0976364796</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lý Công Khang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>095207717245</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khanglc@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0765543972</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lâm Thị Sô Ka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306519287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kalts@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0356284533</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Quốc Huy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084207457636</x:t>
-  </x:si>
-  <x:si>
-    <x:t>huybq@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0358478239</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Châu Yến Trâm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086307418213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tramcy@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0980140725</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cao Kim Mai</x:t>
-  </x:si>
-  <x:si>
-    <x:t>089306828375</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maick@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0933961878</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đặng Hoàng Phát</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086207501341</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phatdh@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0328273063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hồ Trọng Hiếu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205501111</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hieuht@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0383329486</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trương Diễm Hương</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306708343</x:t>
-  </x:si>
-  <x:si>
-    <x:t>huongtd@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0799434505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Bích Nhung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306230754</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhungdb@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0705573756</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Võ Minh Lộc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>087206547340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>locvm@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0906634998</x:t>
-  </x:si>
-  <x:si>
-    <x:t>64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Gia Duy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084207337323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duypg@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0972945557</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mai Thanh Hân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>091307189570</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hanmt2@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0704376698</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mai Diễm Mai</x:t>
-  </x:si>
-  <x:si>
-    <x:t>095306682900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maimd@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0705377769</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Thanh Vy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307183024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>vypt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0977866596</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phan Mỹ Hương</x:t>
-  </x:si>
-  <x:si>
-    <x:t>086306551414</x:t>
-  </x:si>
-  <x:si>
-    <x:t>huongpm@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0321101268</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306635880</x:t>
-  </x:si>
-  <x:si>
-    <x:t>phiadts2@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0985002508</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tạ Bích Ngọc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>083307860204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ngoctb@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0354270093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phạm Hoàng Tài</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206869893</x:t>
-  </x:si>
-  <x:si>
-    <x:t>taiph@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0986334014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>76</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sơn Sa Ruôl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205786003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ruolss@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0768832759</x:t>
-  </x:si>
-  <x:si>
-    <x:t>67</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tạ Phương Châu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>089305962940</x:t>
-  </x:si>
-  <x:si>
-    <x:t>chautp@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0350865639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bùi Nhật Long</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206810306</x:t>
-  </x:si>
-  <x:si>
-    <x:t>longbn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0708690541</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phạm Thu Ngân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084306115440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nganpt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0385117673</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hồ Phương Lan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084307591487</x:t>
-  </x:si>
-  <x:si>
-    <x:t>lanhp@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0948577595</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lý Bích Nhung</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084305174514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhunglb@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0703121935</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ấp Hiếu Trung, Xã Hiếu Tử, Huyện Tiểu Cần, Tỉnh Trà Vinh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sơn Thị Sô Ka</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084305867970</x:t>
-  </x:si>
-  <x:si>
-    <x:t>kasts@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0918529360</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tạ Thị Trâm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084305170110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tramtt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0946583809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sơn Rô Tha Na</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084205905600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nasrt@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0767410798</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Đỗ Ngọc Nhi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>094306888995</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhidn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0941476650</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lê Công Thiện</x:t>
-  </x:si>
-  <x:si>
-    <x:t>092205639988</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thienlc@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0981384507</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ngô Anh Thiện</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206136968</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thienna@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0905452018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cao Ngọc Như</x:t>
-  </x:si>
-  <x:si>
-    <x:t>095305413982</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nhucn@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0355398125</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nguyễn Thanh Bảo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084206462993</x:t>
-  </x:si>
-  <x:si>
-    <x:t>baont@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0917102655</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Châu Diễm Ngân</x:t>
-  </x:si>
-  <x:si>
-    <x:t>092305851812</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ngancd@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0768437124</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Châu Vi Rây</x:t>
-  </x:si>
-  <x:si>
-    <x:t>084207043792</x:t>
-  </x:si>
-  <x:si>
-    <x:t>raycv@st.tvu.edu.vn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0326151026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA25KMB</x:t>
+    <x:t>Huỳnh Văn Hải</x:t>
+  </x:si>
+  <x:si>
+    <x:t>084309663024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hảihv@st.tvu.edu.vn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0981052309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23TTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23TTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KTB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22YDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23YDB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23NHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23NHB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA21KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA22KMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DA23KMB</x:t>
   </x:si>
   <x:si>
     <x:t>DA25NNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21TTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21TTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22TTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22TTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23TTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23TTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21KTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21KTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22KTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22KTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23KTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23KTB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21YDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21YDB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22YDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22YDB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23YDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23YDB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21NHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21NHB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22NHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22NHB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23NHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23NHB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21KMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA21KMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22KMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA22KMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23KMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DA23KMB</x:t>
   </x:si>
   <x:si>
     <x:t>DA21NNA</x:t>
@@ -2355,7 +2358,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1">
-        <x:v>39439</x:v>
+        <x:v>39199</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>16</x:v>
@@ -2382,7 +2385,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="L2" s="2">
-        <x:v>6.01</x:v>
+        <x:v>6.78</x:v>
       </x:c>
       <x:c r="M2" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2399,7 +2402,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="1">
-        <x:v>39226</x:v>
+        <x:v>38895</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>26</x:v>
@@ -2420,13 +2423,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L3" s="2">
-        <x:v>7.26</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="M3" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2437,40 +2440,40 @@
     </x:row>
     <x:row r="4" spans="1:14">
       <x:c r="A4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="C4" s="1">
-        <x:v>38730</x:v>
+        <x:v>38603</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="G4" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
+      <x:c r="I4" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="I4" s="0" t="s">
+      <x:c r="J4" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="K4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L4" s="2">
-        <x:v>6.82</x:v>
+        <x:v>6.68</x:v>
       </x:c>
       <x:c r="M4" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2481,40 +2484,40 @@
     </x:row>
     <x:row r="5" spans="1:14">
       <x:c r="A5" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="C5" s="1">
+        <x:v>39115</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C5" s="1">
-        <x:v>39270</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="F5" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
+      <x:c r="G5" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="H5" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
+      <x:c r="I5" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L5" s="2">
-        <x:v>7.44</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="M5" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2525,40 +2528,40 @@
     </x:row>
     <x:row r="6" spans="1:14">
       <x:c r="A6" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="C6" s="1">
+        <x:v>39270</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C6" s="1">
-        <x:v>38696</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
+      <x:c r="F6" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
+      <x:c r="G6" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="H6" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L6" s="2">
-        <x:v>7.21</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="M6" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2569,40 +2572,40 @@
     </x:row>
     <x:row r="7" spans="1:14">
       <x:c r="A7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>38400</x:v>
+        <x:v>38599</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L7" s="2">
-        <x:v>7.21</x:v>
+        <x:v>6.62</x:v>
       </x:c>
       <x:c r="M7" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2613,40 +2616,40 @@
     </x:row>
     <x:row r="8" spans="1:14">
       <x:c r="A8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>38583</x:v>
+        <x:v>39302</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="L8" s="2">
-        <x:v>8.5</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="M8" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2657,40 +2660,40 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>39055</x:v>
+        <x:v>38933</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="K9" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L9" s="2">
-        <x:v>7.9</x:v>
+        <x:v>8.58</x:v>
       </x:c>
       <x:c r="M9" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2701,40 +2704,40 @@
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>38791</x:v>
+        <x:v>38449</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L10" s="2">
-        <x:v>6.19</x:v>
+        <x:v>6.33</x:v>
       </x:c>
       <x:c r="M10" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2745,40 +2748,40 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>39328</x:v>
+        <x:v>38791</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L11" s="2">
-        <x:v>7.66</x:v>
+        <x:v>6.19</x:v>
       </x:c>
       <x:c r="M11" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2789,40 +2792,40 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>38494</x:v>
+        <x:v>39439</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J12" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L12" s="2">
-        <x:v>7.98</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="M12" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2839,10 +2842,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>38767</x:v>
+        <x:v>39404</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>98</x:v>
@@ -2854,19 +2857,19 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L13" s="2">
-        <x:v>7.32</x:v>
+        <x:v>7.62</x:v>
       </x:c>
       <x:c r="M13" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2877,40 +2880,40 @@
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>38732</x:v>
+        <x:v>38860</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J14" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L14" s="2">
-        <x:v>7.44</x:v>
+        <x:v>6.57</x:v>
       </x:c>
       <x:c r="M14" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2921,40 +2924,40 @@
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>38948</x:v>
+        <x:v>38801</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="K15" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L15" s="2">
-        <x:v>5.03</x:v>
+        <x:v>9.11</x:v>
       </x:c>
       <x:c r="M15" s="3">
         <x:v>46304.6390755903</x:v>
@@ -2965,40 +2968,40 @@
     </x:row>
     <x:row r="16" spans="1:14">
       <x:c r="A16" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>38973</x:v>
+        <x:v>38948</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H16" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L16" s="2">
-        <x:v>6.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="M16" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3009,40 +3012,40 @@
     </x:row>
     <x:row r="17" spans="1:14">
       <x:c r="A17" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>38944</x:v>
+        <x:v>38489</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L17" s="2">
-        <x:v>6.16</x:v>
+        <x:v>7.83</x:v>
       </x:c>
       <x:c r="M17" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3053,40 +3056,40 @@
     </x:row>
     <x:row r="18" spans="1:14">
       <x:c r="A18" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>38902</x:v>
+        <x:v>39223</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L18" s="2">
-        <x:v>7.7</x:v>
+        <x:v>6.92</x:v>
       </x:c>
       <x:c r="M18" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3103,10 +3106,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>39342</x:v>
+        <x:v>38972</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>137</x:v>
@@ -3118,19 +3121,19 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="J19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L19" s="2">
-        <x:v>7.47</x:v>
+        <x:v>8.68</x:v>
       </x:c>
       <x:c r="M19" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3147,7 +3150,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>39340</x:v>
+        <x:v>38494</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>26</x:v>
@@ -3168,13 +3171,13 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L20" s="2">
-        <x:v>7.26</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="M20" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3191,7 +3194,7 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>38738</x:v>
+        <x:v>38710</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>16</x:v>
@@ -3209,16 +3212,16 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L21" s="2">
-        <x:v>7.27</x:v>
+        <x:v>8.78</x:v>
       </x:c>
       <x:c r="M21" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3229,40 +3232,40 @@
     </x:row>
     <x:row r="22" spans="1:14">
       <x:c r="A22" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>38786</x:v>
+        <x:v>38468</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L22" s="2">
-        <x:v>7.37</x:v>
+        <x:v>5.97</x:v>
       </x:c>
       <x:c r="M22" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3279,7 +3282,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>39195</x:v>
+        <x:v>39328</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>16</x:v>
@@ -3294,19 +3297,19 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L23" s="2">
-        <x:v>6.76</x:v>
+        <x:v>7.66</x:v>
       </x:c>
       <x:c r="M23" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3323,10 +3326,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>38603</x:v>
+        <x:v>38403</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
         <x:v>168</x:v>
@@ -3338,19 +3341,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K24" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L24" s="2">
-        <x:v>6.68</x:v>
+        <x:v>7.12</x:v>
       </x:c>
       <x:c r="M24" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3361,40 +3364,40 @@
     </x:row>
     <x:row r="25" spans="1:14">
       <x:c r="A25" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B25" s="0" t="s">
+      <x:c r="C25" s="1">
+        <x:v>39412</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="C25" s="1">
-        <x:v>38799</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
+      <x:c r="F25" s="0" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="F25" s="0" t="s">
+      <x:c r="G25" s="0" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J25" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L25" s="2">
-        <x:v>7.8</x:v>
+        <x:v>8.2</x:v>
       </x:c>
       <x:c r="M25" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3405,40 +3408,40 @@
     </x:row>
     <x:row r="26" spans="1:14">
       <x:c r="A26" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>38599</x:v>
+        <x:v>38730</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K26" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L26" s="2">
-        <x:v>6.62</x:v>
+        <x:v>6.82</x:v>
       </x:c>
       <x:c r="M26" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3449,40 +3452,40 @@
     </x:row>
     <x:row r="27" spans="1:14">
       <x:c r="A27" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>38489</x:v>
+        <x:v>38913</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J27" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K27" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L27" s="2">
-        <x:v>7.83</x:v>
+        <x:v>5.99</x:v>
       </x:c>
       <x:c r="M27" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3493,40 +3496,40 @@
     </x:row>
     <x:row r="28" spans="1:14">
       <x:c r="A28" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="C28" s="1">
+        <x:v>39437</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C28" s="1">
-        <x:v>38670</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E28" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="F28" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="G28" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="H28" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="I28" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K28" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L28" s="2">
-        <x:v>8.97</x:v>
+        <x:v>7.75</x:v>
       </x:c>
       <x:c r="M28" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3537,40 +3540,40 @@
     </x:row>
     <x:row r="29" spans="1:14">
       <x:c r="A29" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="C29" s="1">
+        <x:v>39353</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="C29" s="1">
-        <x:v>39290</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E29" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H29" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="I29" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L29" s="2">
-        <x:v>7.97</x:v>
+        <x:v>5.54</x:v>
       </x:c>
       <x:c r="M29" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3581,40 +3584,40 @@
     </x:row>
     <x:row r="30" spans="1:14">
       <x:c r="A30" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>38933</x:v>
+        <x:v>38944</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K30" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L30" s="2">
-        <x:v>5.43</x:v>
+        <x:v>6.16</x:v>
       </x:c>
       <x:c r="M30" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3625,40 +3628,40 @@
     </x:row>
     <x:row r="31" spans="1:14">
       <x:c r="A31" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>38843</x:v>
+        <x:v>39305</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L31" s="2">
-        <x:v>6.8</x:v>
+        <x:v>7.56</x:v>
       </x:c>
       <x:c r="M31" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3669,40 +3672,40 @@
     </x:row>
     <x:row r="32" spans="1:14">
       <x:c r="A32" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>39115</x:v>
+        <x:v>38988</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L32" s="2">
-        <x:v>6.58</x:v>
+        <x:v>5.78</x:v>
       </x:c>
       <x:c r="M32" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3713,40 +3716,40 @@
     </x:row>
     <x:row r="33" spans="1:14">
       <x:c r="A33" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>38403</x:v>
+        <x:v>38798</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I33" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L33" s="2">
-        <x:v>7.12</x:v>
+        <x:v>6.51</x:v>
       </x:c>
       <x:c r="M33" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3757,40 +3760,40 @@
     </x:row>
     <x:row r="34" spans="1:14">
       <x:c r="A34" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>38617</x:v>
+        <x:v>38648</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K34" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L34" s="2">
-        <x:v>8.31</x:v>
+        <x:v>7.79</x:v>
       </x:c>
       <x:c r="M34" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3801,40 +3804,40 @@
     </x:row>
     <x:row r="35" spans="1:14">
       <x:c r="A35" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>38546</x:v>
+        <x:v>38853</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L35" s="2">
-        <x:v>6.58</x:v>
+        <x:v>7.16</x:v>
       </x:c>
       <x:c r="M35" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3845,40 +3848,40 @@
     </x:row>
     <x:row r="36" spans="1:14">
       <x:c r="A36" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>39279</x:v>
+        <x:v>38799</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="I36" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="J36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K36" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L36" s="2">
-        <x:v>7.01</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="M36" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3889,40 +3892,40 @@
     </x:row>
     <x:row r="37" spans="1:14">
       <x:c r="A37" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C37" s="1">
+        <x:v>38986</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="C37" s="1">
-        <x:v>38972</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E37" s="0" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="F37" s="0" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="G37" s="0" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H37" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="I37" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="J37" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L37" s="2">
-        <x:v>8.68</x:v>
+        <x:v>8.48</x:v>
       </x:c>
       <x:c r="M37" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3933,40 +3936,40 @@
     </x:row>
     <x:row r="38" spans="1:14">
       <x:c r="A38" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>39175</x:v>
+        <x:v>39000</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="I38" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L38" s="2">
-        <x:v>6.22</x:v>
+        <x:v>8.53</x:v>
       </x:c>
       <x:c r="M38" s="3">
         <x:v>46304.6390755903</x:v>
@@ -3977,40 +3980,40 @@
     </x:row>
     <x:row r="39" spans="1:14">
       <x:c r="A39" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>38943</x:v>
+        <x:v>38767</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G39" s="0" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H39" s="0" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="I39" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="J39" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L39" s="2">
-        <x:v>6.94</x:v>
+        <x:v>7.32</x:v>
       </x:c>
       <x:c r="M39" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4021,40 +4024,40 @@
     </x:row>
     <x:row r="40" spans="1:14">
       <x:c r="A40" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>38798</x:v>
+        <x:v>38890</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K40" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L40" s="2">
-        <x:v>6.51</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="M40" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4065,40 +4068,40 @@
     </x:row>
     <x:row r="41" spans="1:14">
       <x:c r="A41" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C41" s="1">
+        <x:v>38951</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="B41" s="0" t="s">
+      <x:c r="G41" s="0" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="C41" s="1">
-        <x:v>39000</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E41" s="0" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F41" s="0" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G41" s="0" t="s">
-        <x:v>268</x:v>
-      </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K41" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L41" s="2">
-        <x:v>8.53</x:v>
+        <x:v>6.14</x:v>
       </x:c>
       <x:c r="M41" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4109,40 +4112,40 @@
     </x:row>
     <x:row r="42" spans="1:14">
       <x:c r="A42" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>38832</x:v>
+        <x:v>38629</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L42" s="2">
-        <x:v>7.69</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="M42" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4153,40 +4156,40 @@
     </x:row>
     <x:row r="43" spans="1:14">
       <x:c r="A43" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="C43" s="1">
+        <x:v>39371</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="B43" s="0" t="s">
+      <x:c r="H43" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="C43" s="1">
-        <x:v>38838</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E43" s="0" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="F43" s="0" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="G43" s="0" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="H43" s="0" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="I43" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K43" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L43" s="2">
-        <x:v>7.37</x:v>
+        <x:v>7.62</x:v>
       </x:c>
       <x:c r="M43" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4197,40 +4200,40 @@
     </x:row>
     <x:row r="44" spans="1:14">
       <x:c r="A44" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>38933</x:v>
+        <x:v>38419</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="L44" s="2">
-        <x:v>8.58</x:v>
+        <x:v>5.99</x:v>
       </x:c>
       <x:c r="M44" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4241,40 +4244,40 @@
     </x:row>
     <x:row r="45" spans="1:14">
       <x:c r="A45" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C45" s="1">
+        <x:v>38824</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="B45" s="0" t="s">
+      <x:c r="G45" s="0" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="C45" s="1">
-        <x:v>39326</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E45" s="0" t="s">
+      <x:c r="H45" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="F45" s="0" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G45" s="0" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H45" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="I45" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L45" s="2">
-        <x:v>6.79</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="M45" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4285,40 +4288,40 @@
     </x:row>
     <x:row r="46" spans="1:14">
       <x:c r="A46" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="C46" s="1">
+        <x:v>38933</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="B46" s="0" t="s">
+      <x:c r="F46" s="0" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="C46" s="1">
-        <x:v>38402</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E46" s="0" t="s">
+      <x:c r="G46" s="0" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="F46" s="0" t="s">
+      <x:c r="H46" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="G46" s="0" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H46" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I46" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L46" s="2">
-        <x:v>6.46</x:v>
+        <x:v>5.43</x:v>
       </x:c>
       <x:c r="M46" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4329,40 +4332,40 @@
     </x:row>
     <x:row r="47" spans="1:14">
       <x:c r="A47" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>297</x:v>
-      </x:c>
       <x:c r="C47" s="1">
-        <x:v>38971</x:v>
+        <x:v>38400</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="F47" s="0" t="s">
+      <x:c r="G47" s="0" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="G47" s="0" t="s">
+      <x:c r="H47" s="0" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="H47" s="0" t="s">
-        <x:v>301</x:v>
-      </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L47" s="2">
-        <x:v>5.98</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="M47" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4373,40 +4376,40 @@
     </x:row>
     <x:row r="48" spans="1:14">
       <x:c r="A48" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="B48" s="0" t="s">
+      <x:c r="C48" s="1">
+        <x:v>39271</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="C48" s="1">
-        <x:v>39437</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E48" s="0" t="s">
+      <x:c r="F48" s="0" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="F48" s="0" t="s">
+      <x:c r="G48" s="0" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="G48" s="0" t="s">
-        <x:v>306</x:v>
-      </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J48" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L48" s="2">
-        <x:v>7.75</x:v>
+        <x:v>6.44</x:v>
       </x:c>
       <x:c r="M48" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4417,40 +4420,40 @@
     </x:row>
     <x:row r="49" spans="1:14">
       <x:c r="A49" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="B49" s="0" t="s">
+      <x:c r="C49" s="1">
+        <x:v>38921</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="C49" s="1">
-        <x:v>38890</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E49" s="0" t="s">
+      <x:c r="F49" s="0" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="F49" s="0" t="s">
+      <x:c r="G49" s="0" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="G49" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I49" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L49" s="2">
-        <x:v>7.69</x:v>
+        <x:v>6.92</x:v>
       </x:c>
       <x:c r="M49" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4461,40 +4464,40 @@
     </x:row>
     <x:row r="50" spans="1:14">
       <x:c r="A50" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="B50" s="0" t="s">
+      <x:c r="C50" s="1">
+        <x:v>38943</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="C50" s="1">
-        <x:v>38583</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E50" s="0" t="s">
+      <x:c r="F50" s="0" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="F50" s="0" t="s">
+      <x:c r="G50" s="0" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="G50" s="0" t="s">
+      <x:c r="H50" s="0" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="H50" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="I50" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J50" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L50" s="2">
-        <x:v>5.98</x:v>
+        <x:v>6.94</x:v>
       </x:c>
       <x:c r="M50" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4511,10 +4514,10 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>38396</x:v>
+        <x:v>39389</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>319</x:v>
@@ -4526,19 +4529,19 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="J51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L51" s="2">
-        <x:v>7.59</x:v>
+        <x:v>7.08</x:v>
       </x:c>
       <x:c r="M51" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4555,10 +4558,10 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>39405</x:v>
+        <x:v>39015</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>324</x:v>
@@ -4570,19 +4573,19 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I52" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J52" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L52" s="2">
-        <x:v>7.71</x:v>
+        <x:v>7.93</x:v>
       </x:c>
       <x:c r="M52" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4599,10 +4602,10 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="C53" s="1">
-        <x:v>38449</x:v>
+        <x:v>38732</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>329</x:v>
@@ -4614,19 +4617,19 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I53" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J53" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L53" s="2">
-        <x:v>6.33</x:v>
+        <x:v>7.44</x:v>
       </x:c>
       <x:c r="M53" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4643,10 +4646,10 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="C54" s="1">
-        <x:v>38970</x:v>
+        <x:v>39258</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>334</x:v>
@@ -4658,19 +4661,19 @@
         <x:v>336</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="I54" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J54" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L54" s="2">
-        <x:v>6.65</x:v>
+        <x:v>7.01</x:v>
       </x:c>
       <x:c r="M54" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4681,40 +4684,40 @@
     </x:row>
     <x:row r="55" spans="1:14">
       <x:c r="A55" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C55" s="1">
-        <x:v>38363</x:v>
+        <x:v>39099</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="H55" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I55" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="J55" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L55" s="2">
-        <x:v>6.99</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="M55" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4725,40 +4728,40 @@
     </x:row>
     <x:row r="56" spans="1:14">
       <x:c r="A56" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C56" s="1">
-        <x:v>39223</x:v>
+        <x:v>38693</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="I56" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J56" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L56" s="2">
-        <x:v>6.92</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="M56" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4775,7 +4778,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="C57" s="1">
-        <x:v>39302</x:v>
+        <x:v>39342</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>16</x:v>
@@ -4790,19 +4793,19 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="I57" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J57" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L57" s="2">
-        <x:v>5.07</x:v>
+        <x:v>7.47</x:v>
       </x:c>
       <x:c r="M57" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4813,40 +4816,40 @@
     </x:row>
     <x:row r="58" spans="1:14">
       <x:c r="A58" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>39412</x:v>
+        <x:v>38832</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="F58" s="0" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="G58" s="0" t="s">
-        <x:v>359</x:v>
-      </x:c>
       <x:c r="H58" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="I58" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="J58" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="J58" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="K58" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L58" s="2">
-        <x:v>8.2</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="M58" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4857,40 +4860,40 @@
     </x:row>
     <x:row r="59" spans="1:14">
       <x:c r="A59" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>39371</x:v>
+        <x:v>38549</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="F59" s="0" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="G59" s="0" t="s">
-        <x:v>364</x:v>
-      </x:c>
       <x:c r="H59" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I59" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="J59" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L59" s="2">
-        <x:v>7.62</x:v>
+        <x:v>4.88</x:v>
       </x:c>
       <x:c r="M59" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4901,40 +4904,40 @@
     </x:row>
     <x:row r="60" spans="1:14">
       <x:c r="A60" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="C60" s="1">
+        <x:v>38573</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="B60" s="0" t="s">
+      <x:c r="F60" s="0" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="C60" s="1">
-        <x:v>39099</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E60" s="0" t="s">
+      <x:c r="G60" s="0" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="F60" s="0" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="G60" s="0" t="s">
-        <x:v>369</x:v>
-      </x:c>
       <x:c r="H60" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I60" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J60" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L60" s="2">
-        <x:v>6.13</x:v>
+        <x:v>8.77</x:v>
       </x:c>
       <x:c r="M60" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4945,40 +4948,40 @@
     </x:row>
     <x:row r="61" spans="1:14">
       <x:c r="A61" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="C61" s="1">
+        <x:v>38696</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="B61" s="0" t="s">
+      <x:c r="F61" s="0" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="C61" s="1">
-        <x:v>39199</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E61" s="0" t="s">
+      <x:c r="G61" s="0" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="G61" s="0" t="s">
-        <x:v>374</x:v>
-      </x:c>
       <x:c r="H61" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I61" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="J61" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L61" s="2">
-        <x:v>6.78</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="M61" s="3">
         <x:v>46304.6390755903</x:v>
@@ -4989,40 +4992,40 @@
     </x:row>
     <x:row r="62" spans="1:14">
       <x:c r="A62" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C62" s="1">
-        <x:v>38603</x:v>
+        <x:v>39055</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="F62" s="0" t="s">
-        <x:v>378</x:v>
-      </x:c>
-      <x:c r="G62" s="0" t="s">
-        <x:v>379</x:v>
-      </x:c>
       <x:c r="H62" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="I62" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J62" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L62" s="2">
-        <x:v>8.61</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="M62" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5033,40 +5036,40 @@
     </x:row>
     <x:row r="63" spans="1:14">
       <x:c r="A63" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="C63" s="1">
+        <x:v>38970</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="B63" s="0" t="s">
+      <x:c r="F63" s="0" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="C63" s="1">
-        <x:v>38693</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E63" s="0" t="s">
+      <x:c r="G63" s="0" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="F63" s="0" t="s">
+      <x:c r="H63" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="G63" s="0" t="s">
-        <x:v>384</x:v>
-      </x:c>
-      <x:c r="H63" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I63" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="J63" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L63" s="2">
-        <x:v>7.07</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="M63" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5077,40 +5080,40 @@
     </x:row>
     <x:row r="64" spans="1:14">
       <x:c r="A64" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="B64" s="0" t="s">
+      <x:c r="C64" s="1">
+        <x:v>38583</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="C64" s="1">
-        <x:v>38834</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E64" s="0" t="s">
+      <x:c r="F64" s="0" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="F64" s="0" t="s">
+      <x:c r="G64" s="0" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="G64" s="0" t="s">
+      <x:c r="H64" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="H64" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="I64" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
       <x:c r="J64" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K64" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L64" s="2">
-        <x:v>7.6</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="M64" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5127,7 +5130,7 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="C65" s="1">
-        <x:v>38988</x:v>
+        <x:v>39409</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>26</x:v>
@@ -5142,19 +5145,19 @@
         <x:v>394</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I65" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J65" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K65" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L65" s="2">
-        <x:v>5.78</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="M65" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5165,40 +5168,40 @@
     </x:row>
     <x:row r="66" spans="1:14">
       <x:c r="A66" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="B66" s="0" t="s">
+      <x:c r="C66" s="1">
+        <x:v>38493</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="C66" s="1">
-        <x:v>38419</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E66" s="0" t="s">
+      <x:c r="F66" s="0" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="F66" s="0" t="s">
+      <x:c r="G66" s="0" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="G66" s="0" t="s">
-        <x:v>400</x:v>
-      </x:c>
       <x:c r="H66" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="I66" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="J66" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K66" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L66" s="2">
-        <x:v>5.99</x:v>
+        <x:v>7.92</x:v>
       </x:c>
       <x:c r="M66" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5209,40 +5212,40 @@
     </x:row>
     <x:row r="67" spans="1:14">
       <x:c r="A67" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>402</x:v>
-      </x:c>
       <x:c r="C67" s="1">
-        <x:v>38901</x:v>
+        <x:v>38738</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="F67" s="0" t="s">
+      <x:c r="G67" s="0" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="G67" s="0" t="s">
-        <x:v>405</x:v>
-      </x:c>
       <x:c r="H67" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I67" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J67" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K67" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L67" s="2">
-        <x:v>5.41</x:v>
+        <x:v>7.27</x:v>
       </x:c>
       <x:c r="M67" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5253,40 +5256,40 @@
     </x:row>
     <x:row r="68" spans="1:14">
       <x:c r="A68" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>407</x:v>
-      </x:c>
       <x:c r="C68" s="1">
-        <x:v>39218</x:v>
+        <x:v>38361</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="F68" s="0" t="s">
+      <x:c r="G68" s="0" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="G68" s="0" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="H68" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I68" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J68" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K68" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L68" s="2">
-        <x:v>6.3</x:v>
+        <x:v>5.39</x:v>
       </x:c>
       <x:c r="M68" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5297,40 +5300,40 @@
     </x:row>
     <x:row r="69" spans="1:14">
       <x:c r="A69" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="B69" s="0" t="s">
+      <x:c r="C69" s="1">
+        <x:v>38843</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="C69" s="1">
-        <x:v>38860</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E69" s="0" t="s">
+      <x:c r="F69" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
-      <x:c r="F69" s="0" t="s">
+      <x:c r="G69" s="0" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="G69" s="0" t="s">
-        <x:v>415</x:v>
-      </x:c>
       <x:c r="H69" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I69" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K69" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="L69" s="2">
-        <x:v>6.57</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="M69" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5341,40 +5344,40 @@
     </x:row>
     <x:row r="70" spans="1:14">
       <x:c r="A70" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="B70" s="0" t="s">
+      <x:c r="C70" s="1">
+        <x:v>39218</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
         <x:v>417</x:v>
       </x:c>
-      <x:c r="C70" s="1">
-        <x:v>39389</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E70" s="0" t="s">
+      <x:c r="F70" s="0" t="s">
         <x:v>418</x:v>
       </x:c>
-      <x:c r="F70" s="0" t="s">
+      <x:c r="G70" s="0" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="G70" s="0" t="s">
-        <x:v>420</x:v>
-      </x:c>
       <x:c r="H70" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I70" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J70" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K70" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L70" s="2">
-        <x:v>7.08</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="M70" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5385,40 +5388,40 @@
     </x:row>
     <x:row r="71" spans="1:14">
       <x:c r="A71" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>421</x:v>
       </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>422</x:v>
-      </x:c>
       <x:c r="C71" s="1">
-        <x:v>39258</x:v>
+        <x:v>39326</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="F71" s="0" t="s">
+      <x:c r="G71" s="0" t="s">
         <x:v>424</x:v>
       </x:c>
-      <x:c r="G71" s="0" t="s">
-        <x:v>425</x:v>
-      </x:c>
       <x:c r="H71" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I71" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="J71" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K71" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L71" s="2">
-        <x:v>7.01</x:v>
+        <x:v>6.79</x:v>
       </x:c>
       <x:c r="M71" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5429,40 +5432,40 @@
     </x:row>
     <x:row r="72" spans="1:14">
       <x:c r="A72" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>427</x:v>
-      </x:c>
       <x:c r="C72" s="1">
-        <x:v>38921</x:v>
+        <x:v>39084</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="F72" s="0" t="s">
+      <x:c r="G72" s="0" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="G72" s="0" t="s">
-        <x:v>430</x:v>
-      </x:c>
       <x:c r="H72" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="I72" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J72" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K72" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L72" s="2">
-        <x:v>6.92</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="M72" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5473,40 +5476,40 @@
     </x:row>
     <x:row r="73" spans="1:14">
       <x:c r="A73" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="B73" s="0" t="s">
+      <x:c r="C73" s="1">
+        <x:v>38402</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="C73" s="1">
-        <x:v>39084</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E73" s="0" t="s">
+      <x:c r="F73" s="0" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="F73" s="0" t="s">
+      <x:c r="G73" s="0" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="G73" s="0" t="s">
-        <x:v>435</x:v>
-      </x:c>
       <x:c r="H73" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="I73" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J73" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K73" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L73" s="2">
-        <x:v>7.65</x:v>
+        <x:v>6.46</x:v>
       </x:c>
       <x:c r="M73" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5517,40 +5520,40 @@
     </x:row>
     <x:row r="74" spans="1:14">
       <x:c r="A74" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>437</x:v>
-      </x:c>
       <x:c r="C74" s="1">
-        <x:v>38629</x:v>
+        <x:v>39405</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="F74" s="0" t="s">
+      <x:c r="G74" s="0" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="G74" s="0" t="s">
-        <x:v>440</x:v>
-      </x:c>
       <x:c r="H74" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I74" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J74" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K74" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="L74" s="2">
-        <x:v>8.8</x:v>
+        <x:v>7.71</x:v>
       </x:c>
       <x:c r="M74" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5561,40 +5564,40 @@
     </x:row>
     <x:row r="75" spans="1:14">
       <x:c r="A75" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>442</x:v>
-      </x:c>
       <x:c r="C75" s="1">
-        <x:v>39037</x:v>
+        <x:v>38617</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="F75" s="0" t="s">
+      <x:c r="G75" s="0" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="G75" s="0" t="s">
-        <x:v>445</x:v>
-      </x:c>
       <x:c r="H75" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I75" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="J75" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K75" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="L75" s="2">
-        <x:v>8.59</x:v>
+        <x:v>8.31</x:v>
       </x:c>
       <x:c r="M75" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5605,40 +5608,40 @@
     </x:row>
     <x:row r="76" spans="1:14">
       <x:c r="A76" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>447</x:v>
-      </x:c>
       <x:c r="C76" s="1">
-        <x:v>38913</x:v>
+        <x:v>38396</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="F76" s="0" t="s">
+      <x:c r="G76" s="0" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="G76" s="0" t="s">
-        <x:v>450</x:v>
-      </x:c>
       <x:c r="H76" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I76" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J76" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K76" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L76" s="2">
-        <x:v>5.99</x:v>
+        <x:v>7.59</x:v>
       </x:c>
       <x:c r="M76" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5649,40 +5652,40 @@
     </x:row>
     <x:row r="77" spans="1:14">
       <x:c r="A77" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
         <x:v>451</x:v>
       </x:c>
-      <x:c r="B77" s="0" t="s">
+      <x:c r="C77" s="1">
+        <x:v>38479</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="C77" s="1">
-        <x:v>38722</x:v>
-      </x:c>
-      <x:c r="D77" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E77" s="0" t="s">
+      <x:c r="F77" s="0" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="F77" s="0" t="s">
+      <x:c r="G77" s="0" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="G77" s="0" t="s">
-        <x:v>455</x:v>
-      </x:c>
       <x:c r="H77" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="I77" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="J77" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K77" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L77" s="2">
-        <x:v>6.6</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="M77" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5693,40 +5696,40 @@
     </x:row>
     <x:row r="78" spans="1:14">
       <x:c r="A78" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="B78" s="0" t="s">
+      <x:c r="C78" s="1">
+        <x:v>38902</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
         <x:v>457</x:v>
       </x:c>
-      <x:c r="C78" s="1">
-        <x:v>39409</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E78" s="0" t="s">
+      <x:c r="F78" s="0" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="F78" s="0" t="s">
+      <x:c r="G78" s="0" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="G78" s="0" t="s">
-        <x:v>460</x:v>
-      </x:c>
       <x:c r="H78" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="I78" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="J78" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K78" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L78" s="2">
-        <x:v>6.65</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="M78" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5737,40 +5740,40 @@
     </x:row>
     <x:row r="79" spans="1:14">
       <x:c r="A79" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="B79" s="0" t="s">
+      <x:c r="C79" s="1">
+        <x:v>38838</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="C79" s="1">
-        <x:v>39304</x:v>
-      </x:c>
-      <x:c r="D79" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E79" s="0" t="s">
+      <x:c r="F79" s="0" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="F79" s="0" t="s">
+      <x:c r="G79" s="0" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="G79" s="0" t="s">
-        <x:v>465</x:v>
-      </x:c>
       <x:c r="H79" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I79" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="J79" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K79" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L79" s="2">
-        <x:v>7.09</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="M79" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5781,40 +5784,40 @@
     </x:row>
     <x:row r="80" spans="1:14">
       <x:c r="A80" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
         <x:v>466</x:v>
       </x:c>
-      <x:c r="B80" s="0" t="s">
+      <x:c r="C80" s="1">
+        <x:v>39279</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
         <x:v>467</x:v>
       </x:c>
-      <x:c r="C80" s="1">
-        <x:v>38986</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E80" s="0" t="s">
+      <x:c r="F80" s="0" t="s">
         <x:v>468</x:v>
       </x:c>
-      <x:c r="F80" s="0" t="s">
+      <x:c r="G80" s="0" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="G80" s="0" t="s">
-        <x:v>470</x:v>
-      </x:c>
       <x:c r="H80" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I80" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J80" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K80" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L80" s="2">
-        <x:v>8.48</x:v>
+        <x:v>7.01</x:v>
       </x:c>
       <x:c r="M80" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5825,40 +5828,40 @@
     </x:row>
     <x:row r="81" spans="1:14">
       <x:c r="A81" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
         <x:v>471</x:v>
       </x:c>
-      <x:c r="B81" s="0" t="s">
+      <x:c r="C81" s="1">
+        <x:v>38546</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
         <x:v>472</x:v>
       </x:c>
-      <x:c r="C81" s="1">
-        <x:v>39404</x:v>
-      </x:c>
-      <x:c r="D81" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E81" s="0" t="s">
+      <x:c r="F81" s="0" t="s">
         <x:v>473</x:v>
       </x:c>
-      <x:c r="F81" s="0" t="s">
+      <x:c r="G81" s="0" t="s">
         <x:v>474</x:v>
       </x:c>
-      <x:c r="G81" s="0" t="s">
-        <x:v>475</x:v>
-      </x:c>
       <x:c r="H81" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I81" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J81" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K81" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L81" s="2">
-        <x:v>7.62</x:v>
+        <x:v>6.58</x:v>
       </x:c>
       <x:c r="M81" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5869,40 +5872,40 @@
     </x:row>
     <x:row r="82" spans="1:14">
       <x:c r="A82" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>477</x:v>
-      </x:c>
       <x:c r="C82" s="1">
-        <x:v>39015</x:v>
+        <x:v>38722</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="F82" s="0" t="s">
+      <x:c r="G82" s="0" t="s">
         <x:v>479</x:v>
       </x:c>
-      <x:c r="G82" s="0" t="s">
+      <x:c r="H82" s="0" t="s">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="H82" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="I82" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="J82" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K82" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L82" s="2">
-        <x:v>7.93</x:v>
+        <x:v>6.6</x:v>
       </x:c>
       <x:c r="M82" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5916,37 +5919,37 @@
         <x:v>481</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="C83" s="1">
-        <x:v>38801</x:v>
+        <x:v>38583</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="H83" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="I83" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="J83" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="J83" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="K83" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L83" s="2">
-        <x:v>9.11</x:v>
+        <x:v>8.5</x:v>
       </x:c>
       <x:c r="M83" s="3">
         <x:v>46304.6390755903</x:v>
@@ -5957,40 +5960,40 @@
     </x:row>
     <x:row r="84" spans="1:14">
       <x:c r="A84" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="C84" s="1">
-        <x:v>39353</x:v>
+        <x:v>38973</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="H84" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I84" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J84" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K84" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="L84" s="2">
-        <x:v>5.54</x:v>
+        <x:v>6.85</x:v>
       </x:c>
       <x:c r="M84" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6001,40 +6004,40 @@
     </x:row>
     <x:row r="85" spans="1:14">
       <x:c r="A85" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="C85" s="1">
-        <x:v>38824</x:v>
+        <x:v>38670</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="H85" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="I85" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="J85" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K85" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L85" s="2">
-        <x:v>5.13</x:v>
+        <x:v>8.97</x:v>
       </x:c>
       <x:c r="M85" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6045,40 +6048,40 @@
     </x:row>
     <x:row r="86" spans="1:14">
       <x:c r="A86" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="C86" s="1">
-        <x:v>38479</x:v>
+        <x:v>39037</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="H86" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I86" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="J86" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K86" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L86" s="2">
-        <x:v>6.13</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="M86" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6089,40 +6092,40 @@
     </x:row>
     <x:row r="87" spans="1:14">
       <x:c r="A87" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="C87" s="1">
-        <x:v>38361</x:v>
+        <x:v>39175</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="H87" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="I87" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="J87" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="K87" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="L87" s="2">
-        <x:v>5.39</x:v>
+        <x:v>6.22</x:v>
       </x:c>
       <x:c r="M87" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6133,40 +6136,40 @@
     </x:row>
     <x:row r="88" spans="1:14">
       <x:c r="A88" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="C88" s="1">
-        <x:v>38788</x:v>
+        <x:v>38393</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="H88" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I88" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J88" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K88" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L88" s="2">
-        <x:v>8.59</x:v>
+        <x:v>7.07</x:v>
       </x:c>
       <x:c r="M88" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6177,40 +6180,40 @@
     </x:row>
     <x:row r="89" spans="1:14">
       <x:c r="A89" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="C89" s="1">
-        <x:v>38951</x:v>
+        <x:v>39304</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="H89" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="I89" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="J89" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K89" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L89" s="2">
-        <x:v>6.14</x:v>
+        <x:v>7.09</x:v>
       </x:c>
       <x:c r="M89" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6221,40 +6224,40 @@
     </x:row>
     <x:row r="90" spans="1:14">
       <x:c r="A90" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="C90" s="1">
-        <x:v>39271</x:v>
+        <x:v>38763</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="H90" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="I90" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J90" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K90" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L90" s="2">
-        <x:v>6.44</x:v>
+        <x:v>7.74</x:v>
       </x:c>
       <x:c r="M90" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6265,40 +6268,40 @@
     </x:row>
     <x:row r="91" spans="1:14">
       <x:c r="A91" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C91" s="1">
-        <x:v>38710</x:v>
+        <x:v>38788</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="H91" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I91" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J91" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K91" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L91" s="2">
-        <x:v>8.78</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="M91" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6309,40 +6312,40 @@
     </x:row>
     <x:row r="92" spans="1:14">
       <x:c r="A92" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C92" s="1">
-        <x:v>38468</x:v>
+        <x:v>39340</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="H92" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I92" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="J92" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K92" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L92" s="2">
-        <x:v>5.97</x:v>
+        <x:v>7.26</x:v>
       </x:c>
       <x:c r="M92" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6353,40 +6356,40 @@
     </x:row>
     <x:row r="93" spans="1:14">
       <x:c r="A93" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="C93" s="1">
-        <x:v>38648</x:v>
+        <x:v>38603</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="H93" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="I93" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J93" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K93" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="L93" s="2">
-        <x:v>7.79</x:v>
+        <x:v>8.61</x:v>
       </x:c>
       <x:c r="M93" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6397,40 +6400,40 @@
     </x:row>
     <x:row r="94" spans="1:14">
       <x:c r="A94" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="C94" s="1">
-        <x:v>38493</x:v>
+        <x:v>38786</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="H94" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I94" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="J94" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K94" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L94" s="2">
-        <x:v>7.92</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="M94" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6441,40 +6444,40 @@
     </x:row>
     <x:row r="95" spans="1:14">
       <x:c r="A95" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="C95" s="1">
-        <x:v>38853</x:v>
+        <x:v>38901</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="H95" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I95" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="J95" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K95" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L95" s="2">
-        <x:v>7.16</x:v>
+        <x:v>5.41</x:v>
       </x:c>
       <x:c r="M95" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6485,40 +6488,40 @@
     </x:row>
     <x:row r="96" spans="1:14">
       <x:c r="A96" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C96" s="1">
-        <x:v>38549</x:v>
+        <x:v>38971</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="H96" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="I96" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="J96" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K96" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L96" s="2">
-        <x:v>4.88</x:v>
+        <x:v>5.98</x:v>
       </x:c>
       <x:c r="M96" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6529,40 +6532,40 @@
     </x:row>
     <x:row r="97" spans="1:14">
       <x:c r="A97" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="C97" s="1">
-        <x:v>38763</x:v>
+        <x:v>39290</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="H97" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="I97" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J97" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K97" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L97" s="2">
-        <x:v>7.74</x:v>
+        <x:v>7.97</x:v>
       </x:c>
       <x:c r="M97" s="3">
         <x:v>46304.6390755903</x:v>
@@ -6573,178 +6576,178 @@
     </x:row>
     <x:row r="98" spans="1:14">
       <x:c r="A98" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="C98" s="1">
-        <x:v>38573</x:v>
+        <x:v>38862</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="H98" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="I98" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J98" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K98" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L98" s="2">
-        <x:v>8.77</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="M98" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
       <x:c r="N98" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:14">
       <x:c r="A99" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="C99" s="1">
-        <x:v>38895</x:v>
+        <x:v>39224</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="H99" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="I99" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="J99" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K99" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L99" s="2">
-        <x:v>7.8</x:v>
+        <x:v>7.46</x:v>
       </x:c>
       <x:c r="M99" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
       <x:c r="N99" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:14">
       <x:c r="A100" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="C100" s="1">
-        <x:v>38393</x:v>
+        <x:v>38541</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="H100" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="I100" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J100" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K100" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L100" s="2">
-        <x:v>7.07</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="M100" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
       <x:c r="N100" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:14">
       <x:c r="A101" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="C101" s="1">
-        <x:v>39305</x:v>
+        <x:v>38379</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="H101" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="I101" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="J101" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K101" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="L101" s="2">
-        <x:v>7.56</x:v>
+        <x:v>8.35</x:v>
       </x:c>
       <x:c r="M101" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
       <x:c r="N101" s="3">
-        <x:v>46304.6390755903</x:v>
+        <x:v>46304.9020702778</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6761,10 +6764,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B29"/>
+  <x:dimension ref="A1:B71"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="48.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="9.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -6778,231 +6781,231 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>579</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>580</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>582</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>583</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>584</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>585</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>586</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>587</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>589</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>590</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>592</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>593</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
       <x:c r="A29" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>594</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
       <x:c r="A30" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>578</x:v>
@@ -7010,330 +7013,330 @@
     </x:row>
     <x:row r="31" spans="1:2">
       <x:c r="A31" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>595</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
       <x:c r="A32" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>389</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
       <x:c r="A33" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
       <x:c r="A34" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
       <x:c r="A35" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
       <x:c r="A36" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>596</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
       <x:c r="A37" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>597</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
       <x:c r="A38" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>598</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
       <x:c r="A39" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>599</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
       <x:c r="A40" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
       <x:c r="A41" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>601</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
       <x:c r="A42" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>255</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
       <x:c r="A43" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
       <x:c r="A44" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
       <x:c r="A45" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:2">
       <x:c r="A46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>602</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:2">
       <x:c r="A47" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
       <x:c r="A48" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>604</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
       <x:c r="A49" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>605</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
       <x:c r="A50" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>606</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
       <x:c r="A51" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>607</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:2">
       <x:c r="A52" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:2">
       <x:c r="A53" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:2">
       <x:c r="A54" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>608</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:2">
       <x:c r="A55" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:2">
       <x:c r="A56" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>609</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:2">
       <x:c r="A57" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>610</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:2">
       <x:c r="A58" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>611</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:2">
       <x:c r="A59" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>612</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:2">
       <x:c r="A60" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>613</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:2">
       <x:c r="A61" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>614</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:2">
       <x:c r="A62" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:2">
       <x:c r="A63" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:2">
       <x:c r="A64" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:2">
       <x:c r="A65" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:2">
       <x:c r="A66" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>614</x:v>
+        <x:v>615</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:2">
       <x:c r="A67" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>615</x:v>
+        <x:v>616</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:2">
       <x:c r="A68" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>616</x:v>
+        <x:v>617</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:2">
       <x:c r="A69" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>617</x:v>
+        <x:v>618</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:2">
       <x:c r="A70" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>618</x:v>
+        <x:v>619</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:2">
       <x:c r="A71" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>619</x:v>
+        <x:v>620</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
